--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/01_raw_results/outputs_IAEE_2025_run_2021.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/01_raw_results/outputs_IAEE_2025_run_2021.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jfg.eco\Documents\GitHub\hydrogen_grid\01_data\02_output_data\02_unidirectional_results\01_paper_IAEE\01_raw_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43B6280-F030-46D3-9AA1-085CE67E6634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF101CD-2606-4CF5-A54E-996C03D7BA83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="433">
   <si>
     <t>Commodity</t>
   </si>
@@ -37,385 +37,436 @@
     <t>Methane</t>
   </si>
   <si>
+    <t>('DK', 'SE')</t>
+  </si>
+  <si>
+    <t>('UK', 'IE')</t>
+  </si>
+  <si>
+    <t>('DE', 'BE')</t>
+  </si>
+  <si>
+    <t>('HU', 'RO')</t>
+  </si>
+  <si>
+    <t>('AT', 'DE')</t>
+  </si>
+  <si>
+    <t>('BG', 'EL')</t>
+  </si>
+  <si>
+    <t>('FR', 'CH')</t>
+  </si>
+  <si>
+    <t>('BE', 'FR')</t>
+  </si>
+  <si>
+    <t>('BG', 'TR')</t>
+  </si>
+  <si>
+    <t>('IT', 'CH')</t>
+  </si>
+  <si>
+    <t>('NO', 'DE')</t>
+  </si>
+  <si>
+    <t>('SI', 'IT')</t>
+  </si>
+  <si>
+    <t>('SK', 'AT')</t>
+  </si>
+  <si>
+    <t>('NO', 'BE')</t>
+  </si>
+  <si>
+    <t>('DE', 'FR')</t>
+  </si>
+  <si>
+    <t>('CH', 'DE')</t>
+  </si>
+  <si>
+    <t>('MD', 'UA')</t>
+  </si>
+  <si>
+    <t>('LT', 'RU')</t>
+  </si>
+  <si>
+    <t>('FR', 'ES')</t>
+  </si>
+  <si>
+    <t>('UA', 'RO')</t>
+  </si>
+  <si>
+    <t>('HU', 'SK')</t>
+  </si>
+  <si>
+    <t>('NO', 'FR')</t>
+  </si>
+  <si>
+    <t>('LT', 'PL')</t>
+  </si>
+  <si>
+    <t>('CH', 'FR')</t>
+  </si>
+  <si>
+    <t>('TR', 'BG')</t>
+  </si>
+  <si>
+    <t>('NL', 'UK')</t>
+  </si>
+  <si>
+    <t>('MA', 'ES')</t>
+  </si>
+  <si>
+    <t>('EE', 'FI')</t>
+  </si>
+  <si>
+    <t>('AT', 'SI')</t>
+  </si>
+  <si>
+    <t>('LV', 'RU')</t>
+  </si>
+  <si>
+    <t>('PT', 'ES')</t>
+  </si>
+  <si>
+    <t>('RO', 'BG')</t>
+  </si>
+  <si>
+    <t>('EL', 'AL')</t>
+  </si>
+  <si>
+    <t>('SK', 'PL')</t>
+  </si>
+  <si>
+    <t>('UK', 'NL')</t>
+  </si>
+  <si>
+    <t>('FI', 'EE')</t>
+  </si>
+  <si>
+    <t>('RU', 'UA')</t>
+  </si>
+  <si>
+    <t>('AL', 'IT')</t>
+  </si>
+  <si>
+    <t>('PL', 'SK')</t>
+  </si>
+  <si>
+    <t>('BG', 'MK')</t>
+  </si>
+  <si>
+    <t>('RS', 'BG')</t>
+  </si>
+  <si>
+    <t>('CZ', 'PL')</t>
+  </si>
+  <si>
+    <t>('EL', 'BG')</t>
+  </si>
+  <si>
+    <t>('BG', 'RO')</t>
+  </si>
+  <si>
+    <t>('DK', 'PL')</t>
+  </si>
+  <si>
+    <t>('TN', 'IT')</t>
+  </si>
+  <si>
+    <t>('LY', 'IT')</t>
+  </si>
+  <si>
+    <t>('DZ', 'TN')</t>
+  </si>
+  <si>
+    <t>('DE', 'AT')</t>
+  </si>
+  <si>
+    <t>('BE', 'UK')</t>
+  </si>
+  <si>
+    <t>('RO', 'HU')</t>
+  </si>
+  <si>
+    <t>('TR', 'EL')</t>
+  </si>
+  <si>
+    <t>('HR', 'SI')</t>
+  </si>
+  <si>
+    <t>('DE', 'DK')</t>
+  </si>
+  <si>
+    <t>('HU', 'HR')</t>
+  </si>
+  <si>
+    <t>('RU', 'DE')</t>
+  </si>
+  <si>
+    <t>('DE', 'CH')</t>
+  </si>
+  <si>
+    <t>('DE', 'CZ')</t>
+  </si>
+  <si>
+    <t>('AT', 'IT')</t>
+  </si>
+  <si>
+    <t>('NO', 'DK')</t>
+  </si>
+  <si>
+    <t>('RS', 'HU')</t>
+  </si>
+  <si>
+    <t>('UK', 'BE')</t>
+  </si>
+  <si>
+    <t>('SK', 'UA')</t>
+  </si>
+  <si>
+    <t>('CH', 'IT')</t>
+  </si>
+  <si>
+    <t>('PL', 'DE')</t>
+  </si>
+  <si>
+    <t>('HR', 'HU')</t>
+  </si>
+  <si>
+    <t>('RU', 'TR')</t>
+  </si>
+  <si>
+    <t>('CZ', 'SK')</t>
+  </si>
+  <si>
+    <t>('DK', 'DE')</t>
+  </si>
+  <si>
+    <t>('UA', 'PL')</t>
+  </si>
+  <si>
+    <t>('BY', 'PL')</t>
+  </si>
+  <si>
+    <t>('AT', 'HU')</t>
+  </si>
+  <si>
+    <t>('LT', 'LV')</t>
+  </si>
+  <si>
+    <t>('FR', 'DE')</t>
+  </si>
+  <si>
+    <t>('RO', 'MD')</t>
+  </si>
+  <si>
+    <t>('FR', 'BE')</t>
+  </si>
+  <si>
+    <t>('BE', 'LU')</t>
+  </si>
+  <si>
+    <t>('RU', 'FI')</t>
+  </si>
+  <si>
+    <t>('HU', 'RS')</t>
+  </si>
+  <si>
+    <t>('LV', 'LT')</t>
+  </si>
+  <si>
+    <t>('MD', 'RO')</t>
+  </si>
+  <si>
+    <t>('LV', 'EE')</t>
+  </si>
+  <si>
+    <t>('RU', 'LV')</t>
+  </si>
+  <si>
+    <t>('RS', 'BA')</t>
+  </si>
+  <si>
+    <t>('NO', 'UK')</t>
+  </si>
+  <si>
+    <t>('DZ', 'ES')</t>
+  </si>
+  <si>
+    <t>('BE', 'NL')</t>
+  </si>
+  <si>
+    <t>('DZ', 'MA')</t>
+  </si>
+  <si>
+    <t>('UA', 'HU')</t>
+  </si>
+  <si>
+    <t>('DE', 'NL')</t>
+  </si>
+  <si>
+    <t>('NL', 'DE')</t>
+  </si>
+  <si>
+    <t>('IT', 'SI')</t>
+  </si>
+  <si>
+    <t>('NL', 'BE')</t>
+  </si>
+  <si>
+    <t>('CZ', 'DE')</t>
+  </si>
+  <si>
+    <t>('AT', 'SK')</t>
+  </si>
+  <si>
+    <t>('DE', 'PL')</t>
+  </si>
+  <si>
+    <t>('RU', 'BY')</t>
+  </si>
+  <si>
+    <t>('NO', 'NL')</t>
+  </si>
+  <si>
+    <t>('BY', 'UA')</t>
+  </si>
+  <si>
+    <t>('ES', 'FR')</t>
+  </si>
+  <si>
+    <t>('SK', 'CZ')</t>
+  </si>
+  <si>
     <t>('DE', 'LU')</t>
   </si>
   <si>
-    <t>('DZ', 'ES')</t>
+    <t>('ES', 'PT')</t>
+  </si>
+  <si>
+    <t>('PL', 'DK')</t>
+  </si>
+  <si>
+    <t>('RO', 'UA')</t>
+  </si>
+  <si>
+    <t>('SI', 'HR')</t>
+  </si>
+  <si>
+    <t>('UA', 'SK')</t>
   </si>
   <si>
     <t>('UA', 'MD')</t>
   </si>
   <si>
-    <t>('DK', 'DE')</t>
-  </si>
-  <si>
-    <t>('MD', 'RO')</t>
-  </si>
-  <si>
-    <t>('DZ', 'TN')</t>
-  </si>
-  <si>
-    <t>('DE', 'PL')</t>
-  </si>
-  <si>
-    <t>('BE', 'FR')</t>
-  </si>
-  <si>
-    <t>('RU', 'LV')</t>
+    <t>('BG', 'RS')</t>
+  </si>
+  <si>
+    <t>('LU', 'BE')</t>
+  </si>
+  <si>
+    <t>('SK', 'HU')</t>
+  </si>
+  <si>
+    <t>('BY', 'LT')</t>
   </si>
   <si>
     <t>('EE', 'LV')</t>
   </si>
   <si>
-    <t>('LT', 'LV')</t>
-  </si>
-  <si>
-    <t>('NO', 'NL')</t>
-  </si>
-  <si>
-    <t>('DE', 'DK')</t>
-  </si>
-  <si>
-    <t>('FR', 'ES')</t>
-  </si>
-  <si>
-    <t>('RO', 'BG')</t>
-  </si>
-  <si>
-    <t>('BG', 'MK')</t>
-  </si>
-  <si>
-    <t>('RU', 'DE')</t>
-  </si>
-  <si>
-    <t>('BY', 'PL')</t>
-  </si>
-  <si>
-    <t>('ES', 'FR')</t>
-  </si>
-  <si>
-    <t>('NO', 'DE')</t>
-  </si>
-  <si>
-    <t>('TR', 'EL')</t>
-  </si>
-  <si>
-    <t>('CH', 'DE')</t>
-  </si>
-  <si>
-    <t>('BG', 'RS')</t>
-  </si>
-  <si>
-    <t>('CZ', 'PL')</t>
-  </si>
-  <si>
-    <t>('IT', 'SI')</t>
-  </si>
-  <si>
-    <t>('AL', 'IT')</t>
-  </si>
-  <si>
-    <t>('NO', 'BE')</t>
-  </si>
-  <si>
-    <t>('PL', 'DE')</t>
-  </si>
-  <si>
-    <t>('NL', 'BE')</t>
-  </si>
-  <si>
-    <t>('CZ', 'SK')</t>
-  </si>
-  <si>
-    <t>('BE', 'UK')</t>
-  </si>
-  <si>
-    <t>('AT', 'IT')</t>
-  </si>
-  <si>
-    <t>('RO', 'MD')</t>
-  </si>
-  <si>
-    <t>('UK', 'NL')</t>
-  </si>
-  <si>
-    <t>('HR', 'HU')</t>
-  </si>
-  <si>
-    <t>('FR', 'BE')</t>
-  </si>
-  <si>
-    <t>('ES', 'PT')</t>
-  </si>
-  <si>
-    <t>('DE', 'NL')</t>
-  </si>
-  <si>
-    <t>('AT', 'HU')</t>
-  </si>
-  <si>
-    <t>('RS', 'HU')</t>
-  </si>
-  <si>
-    <t>('RU', 'FI')</t>
-  </si>
-  <si>
-    <t>('BY', 'LT')</t>
-  </si>
-  <si>
-    <t>('SI', 'IT')</t>
-  </si>
-  <si>
-    <t>('BG', 'TR')</t>
-  </si>
-  <si>
-    <t>('SK', 'AT')</t>
-  </si>
-  <si>
-    <t>('BG', 'EL')</t>
-  </si>
-  <si>
-    <t>('LV', 'RU')</t>
-  </si>
-  <si>
-    <t>('MD', 'UA')</t>
-  </si>
-  <si>
-    <t>('EL', 'BG')</t>
-  </si>
-  <si>
-    <t>('BG', 'RO')</t>
-  </si>
-  <si>
-    <t>('UK', 'IE')</t>
-  </si>
-  <si>
-    <t>('BE', 'LU')</t>
-  </si>
-  <si>
-    <t>('NO', 'UK')</t>
-  </si>
-  <si>
-    <t>('LV', 'EE')</t>
-  </si>
-  <si>
-    <t>('NL', 'UK')</t>
-  </si>
-  <si>
-    <t>('NO', 'FR')</t>
-  </si>
-  <si>
-    <t>('DE', 'BE')</t>
-  </si>
-  <si>
-    <t>('RS', 'BA')</t>
-  </si>
-  <si>
-    <t>('RU', 'BY')</t>
-  </si>
-  <si>
-    <t>('CH', 'FR')</t>
-  </si>
-  <si>
-    <t>('HU', 'RS')</t>
-  </si>
-  <si>
-    <t>('MA', 'ES')</t>
-  </si>
-  <si>
-    <t>('CH', 'IT')</t>
-  </si>
-  <si>
-    <t>('AT', 'SK')</t>
-  </si>
-  <si>
-    <t>('LT', 'RU')</t>
-  </si>
-  <si>
-    <t>('RS', 'BG')</t>
-  </si>
-  <si>
-    <t>('LY', 'IT')</t>
-  </si>
-  <si>
-    <t>('PT', 'ES')</t>
-  </si>
-  <si>
-    <t>('DK', 'SE')</t>
-  </si>
-  <si>
-    <t>('CZ', 'DE')</t>
-  </si>
-  <si>
-    <t>('SK', 'UA')</t>
-  </si>
-  <si>
-    <t>('EL', 'AL')</t>
-  </si>
-  <si>
-    <t>('AT', 'DE')</t>
-  </si>
-  <si>
-    <t>('RU', 'UA')</t>
-  </si>
-  <si>
-    <t>('EE', 'FI')</t>
-  </si>
-  <si>
-    <t>('UA', 'PL')</t>
-  </si>
-  <si>
-    <t>('FI', 'EE')</t>
-  </si>
-  <si>
-    <t>('SK', 'CZ')</t>
+    <t>('BE', 'DE')</t>
   </si>
   <si>
     <t>('IT', 'AT')</t>
   </si>
   <si>
-    <t>('RO', 'UA')</t>
-  </si>
-  <si>
-    <t>('HU', 'SK')</t>
-  </si>
-  <si>
-    <t>('HR', 'SI')</t>
-  </si>
-  <si>
-    <t>('FR', 'CH')</t>
-  </si>
-  <si>
-    <t>('BE', 'DE')</t>
-  </si>
-  <si>
-    <t>('TN', 'IT')</t>
-  </si>
-  <si>
-    <t>('UK', 'BE')</t>
-  </si>
-  <si>
-    <t>('DZ', 'MA')</t>
-  </si>
-  <si>
-    <t>('AT', 'SI')</t>
-  </si>
-  <si>
-    <t>('UA', 'SK')</t>
-  </si>
-  <si>
-    <t>('DE', 'CZ')</t>
-  </si>
-  <si>
-    <t>('DE', 'AT')</t>
-  </si>
-  <si>
-    <t>('IT', 'CH')</t>
-  </si>
-  <si>
-    <t>('DE', 'FR')</t>
-  </si>
-  <si>
-    <t>('BY', 'UA')</t>
-  </si>
-  <si>
-    <t>('HU', 'RO')</t>
-  </si>
-  <si>
-    <t>('TR', 'BG')</t>
-  </si>
-  <si>
-    <t>('SK', 'HU')</t>
-  </si>
-  <si>
-    <t>('UA', 'HU')</t>
-  </si>
-  <si>
-    <t>('LV', 'LT')</t>
-  </si>
-  <si>
-    <t>('LU', 'BE')</t>
-  </si>
-  <si>
-    <t>('DE', 'CH')</t>
-  </si>
-  <si>
-    <t>('RU', 'TR')</t>
-  </si>
-  <si>
-    <t>('BE', 'NL')</t>
-  </si>
-  <si>
-    <t>('UA', 'RO')</t>
-  </si>
-  <si>
-    <t>('SI', 'HR')</t>
-  </si>
-  <si>
-    <t>('HU', 'HR')</t>
-  </si>
-  <si>
-    <t>('RO', 'HU')</t>
-  </si>
-  <si>
-    <t>('NL', 'DE')</t>
+    <t>('EE_LNG_imp', 'EE')</t>
+  </si>
+  <si>
+    <t>('UK_LNG_imp', 'UK')</t>
+  </si>
+  <si>
+    <t>('IT_LNG_imp', 'IT')</t>
+  </si>
+  <si>
+    <t>('PL_LNG_imp', 'PL')</t>
+  </si>
+  <si>
+    <t>('DE_LNG_imp', 'DE')</t>
+  </si>
+  <si>
+    <t>('IE_LNG_imp', 'IE')</t>
+  </si>
+  <si>
+    <t>('HR_LNG_imp', 'HR')</t>
+  </si>
+  <si>
+    <t>('TR_LNG_imp', 'TR')</t>
+  </si>
+  <si>
+    <t>('LV_LNG_imp', 'LV')</t>
+  </si>
+  <si>
+    <t>('ES_LNG_imp', 'ES')</t>
+  </si>
+  <si>
+    <t>('FR_LNG_imp', 'FR')</t>
+  </si>
+  <si>
+    <t>('PT_LNG_imp', 'PT')</t>
+  </si>
+  <si>
+    <t>('NL_LNG_imp', 'NL')</t>
+  </si>
+  <si>
+    <t>('FI_LNG_imp', 'FI')</t>
+  </si>
+  <si>
+    <t>('EL_LNG_imp', 'EL')</t>
+  </si>
+  <si>
+    <t>('BE_LNG_imp', 'BE')</t>
   </si>
   <si>
     <t>('LT_LNG_imp', 'LT')</t>
   </si>
   <si>
-    <t>('BE_LNG_imp', 'BE')</t>
-  </si>
-  <si>
-    <t>('FR_LNG_imp', 'FR')</t>
-  </si>
-  <si>
-    <t>('TR_LNG_imp', 'TR')</t>
-  </si>
-  <si>
-    <t>('IT_LNG_imp', 'IT')</t>
-  </si>
-  <si>
-    <t>('HR_LNG_imp', 'HR')</t>
-  </si>
-  <si>
-    <t>('PT_LNG_imp', 'PT')</t>
-  </si>
-  <si>
-    <t>('PL_LNG_imp', 'PL')</t>
-  </si>
-  <si>
-    <t>('EL_LNG_imp', 'EL')</t>
-  </si>
-  <si>
-    <t>('UK_LNG_imp', 'UK')</t>
-  </si>
-  <si>
-    <t>('ES_LNG_imp', 'ES')</t>
-  </si>
-  <si>
-    <t>('NL_LNG_imp', 'NL')</t>
-  </si>
-  <si>
     <t>('EG_LNG_imp', 'EG')</t>
   </si>
   <si>
+    <t>('IN_LNG_imp', 'IN')</t>
+  </si>
+  <si>
     <t>('SA_LNG_imp', 'SA')</t>
   </si>
   <si>
+    <t>('JS_LNG_imp', 'JS')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_imp', 'AF')</t>
+  </si>
+  <si>
     <t>('AS_LNG_imp', 'AS')</t>
   </si>
   <si>
-    <t>('IN_LNG_imp', 'IN')</t>
-  </si>
-  <si>
     <t>('CN_LNG_imp', 'CN')</t>
   </si>
   <si>
-    <t>('JS_LNG_imp', 'JS')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_imp', 'AF')</t>
+    <t>('IM', 'IM_LNG_exp')</t>
+  </si>
+  <si>
+    <t>('AU', 'AU_LNG_exp')</t>
+  </si>
+  <si>
+    <t>('EG', 'EG_LNG_exp')</t>
+  </si>
+  <si>
+    <t>('QA', 'QA_LNG_exp')</t>
+  </si>
+  <si>
+    <t>('USA', 'USA_LNG_exp')</t>
   </si>
   <si>
     <t>('RU', 'RU_LNG_exp')</t>
@@ -424,565 +475,685 @@
     <t>('ME', 'ME_LNG_exp')</t>
   </si>
   <si>
-    <t>('AU', 'AU_LNG_exp')</t>
-  </si>
-  <si>
-    <t>('QA', 'QA_LNG_exp')</t>
-  </si>
-  <si>
-    <t>('IM', 'IM_LNG_exp')</t>
+    <t>('TT', 'TT_LNG_exp')</t>
   </si>
   <si>
     <t>('AF', 'AF_LNG_exp')</t>
   </si>
   <si>
-    <t>('USA', 'USA_LNG_exp')</t>
-  </si>
-  <si>
-    <t>('TT', 'TT_LNG_exp')</t>
-  </si>
-  <si>
-    <t>('EG', 'EG_LNG_exp')</t>
+    <t>('USA', 'CM')</t>
+  </si>
+  <si>
+    <t>('ME', 'AF')</t>
+  </si>
+  <si>
+    <t>('QA', 'ME')</t>
+  </si>
+  <si>
+    <t>('ME', 'CR')</t>
+  </si>
+  <si>
+    <t>('AS', 'CN')</t>
+  </si>
+  <si>
+    <t>('CM', 'USA')</t>
+  </si>
+  <si>
+    <t>('CR', 'CN')</t>
+  </si>
+  <si>
+    <t>('RU', 'CR')</t>
   </si>
   <si>
     <t>('RU', 'CN')</t>
   </si>
   <si>
-    <t>('USA', 'CM')</t>
+    <t>('CR', 'TR')</t>
   </si>
   <si>
     <t>('ME', 'QA')</t>
   </si>
   <si>
-    <t>('ME', 'CR')</t>
-  </si>
-  <si>
-    <t>('AS', 'CN')</t>
-  </si>
-  <si>
-    <t>('QA', 'ME')</t>
-  </si>
-  <si>
-    <t>('CR', 'TR')</t>
-  </si>
-  <si>
-    <t>('CR', 'CN')</t>
-  </si>
-  <si>
-    <t>('ME', 'AF')</t>
-  </si>
-  <si>
-    <t>('CM', 'USA')</t>
-  </si>
-  <si>
-    <t>('RU', 'CR')</t>
+    <t>('RU_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'EL_LNG_imp')</t>
   </si>
   <si>
     <t>('QA_LNG_exp', 'PL_LNG_imp')</t>
   </si>
   <si>
+    <t>('AF_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
     <t>('AF_LNG_exp', 'SA_LNG_imp')</t>
   </si>
   <si>
+    <t>('USA_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'BE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'JS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'IN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
     <t>('AF_LNG_exp', 'NL_LNG_imp')</t>
   </si>
   <si>
+    <t>('AF_LNG_exp', 'TR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'PT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'AF_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
     <t>('RU_LNG_exp', 'AF_LNG_imp')</t>
   </si>
   <si>
+    <t>('TT_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'LV_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'PL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('QA_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'IT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AU_LNG_exp', 'EG_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'LT_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'EE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'ES_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'EL_LNG_imp')</t>
+  </si>
+  <si>
     <t>('EG_LNG_exp', 'EL_LNG_imp')</t>
   </si>
   <si>
-    <t>('IM_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'PT_LNG_imp')</t>
+    <t>('USA_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'AS_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'DE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'HR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('ME_LNG_exp', 'CN_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('TT_LNG_exp', 'FI_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'FR_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('IM_LNG_exp', 'NL_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'UK_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('USA_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('RU_LNG_exp', 'IE_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('EG_LNG_exp', 'SA_LNG_imp')</t>
+  </si>
+  <si>
+    <t>('AF_LNG_exp', 'AS_LNG_imp')</t>
   </si>
   <si>
     <t>('RU_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'ES_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'JS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'PL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'IN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'TR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'HR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('TT_LNG_exp', 'LT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'EG_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('RU_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'EL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'BE_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AU_LNG_exp', 'AS_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('IM_LNG_exp', 'CN_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('QA_LNG_exp', 'IT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'FR_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'NL_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('USA_LNG_exp', 'SA_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('AF_LNG_exp', 'UK_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'PT_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('EG_LNG_exp', 'AF_LNG_imp')</t>
-  </si>
-  <si>
-    <t>('ME_LNG_exp', 'SA_LNG_imp')</t>
   </si>
   <si>
     <t>('AL_Prod', 'AL')</t>
@@ -1510,7 +1681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D372"/>
+  <dimension ref="A1:D429"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.35">
@@ -1535,10 +1706,10 @@
         <v>5</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6997.2659465473271</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>0.63901972114587458</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
@@ -1549,10 +1720,10 @@
         <v>6</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>11163.69681353934</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>7.9442781096170367E-2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
@@ -1563,10 +1734,10 @@
         <v>7</v>
       </c>
       <c r="C4">
-        <v>1117.368709865174</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1.198339642314117E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
@@ -1605,10 +1776,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>364986.81670725631</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.87862567559067184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
@@ -1619,10 +1790,10 @@
         <v>11</v>
       </c>
       <c r="C8">
-        <v>85227.5</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -1661,10 +1832,10 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>17145.233185288191</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>0.1211118772812409</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -1675,10 +1846,10 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>16018.071319999999</v>
+        <v>447490</v>
       </c>
       <c r="D12">
-        <v>0.64918826781227201</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -1689,10 +1860,10 @@
         <v>16</v>
       </c>
       <c r="C13">
-        <v>351714</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
@@ -1703,10 +1874,10 @@
         <v>17</v>
       </c>
       <c r="C14">
-        <v>18425.94820709651</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0.37088610763530178</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
@@ -1717,10 +1888,10 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>27987.087214615171</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>0.16919009548305</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
@@ -1745,10 +1916,10 @@
         <v>20</v>
       </c>
       <c r="C17">
-        <v>3174.72765343728</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0.31767289927026832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -1787,10 +1958,10 @@
         <v>23</v>
       </c>
       <c r="C20">
-        <v>81906</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -1801,10 +1972,10 @@
         <v>24</v>
       </c>
       <c r="C21">
-        <v>455155</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -1815,10 +1986,10 @@
         <v>25</v>
       </c>
       <c r="C22">
-        <v>75554.49584221284</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0.52404713606528763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
@@ -1829,10 +2000,10 @@
         <v>26</v>
       </c>
       <c r="C23">
-        <v>27549.518082157891</v>
+        <v>8321.9529403805373</v>
       </c>
       <c r="D23">
-        <v>0.43679474381909389</v>
+        <v>4.0105314106483228E-2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
@@ -1843,10 +2014,10 @@
         <v>27</v>
       </c>
       <c r="C24">
-        <v>111067.96169934981</v>
+        <v>21195.258000000002</v>
       </c>
       <c r="D24">
-        <v>0.76431262521706622</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
@@ -1857,10 +2028,10 @@
         <v>28</v>
       </c>
       <c r="C25">
-        <v>5357.0415666666886</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0.52417236464449013</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
@@ -1871,10 +2042,10 @@
         <v>29</v>
       </c>
       <c r="C26">
-        <v>8302.8058205838261</v>
+        <v>49019.922124767683</v>
       </c>
       <c r="D26">
-        <v>0.79815484937119208</v>
+        <v>0.23314958683786061</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
@@ -1885,10 +2056,10 @@
         <v>30</v>
       </c>
       <c r="C27">
-        <v>79762.947949686146</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>0.44863195343807849</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
@@ -1899,10 +2070,10 @@
         <v>31</v>
       </c>
       <c r="C28">
-        <v>167754</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
@@ -1941,10 +2112,10 @@
         <v>34</v>
       </c>
       <c r="C31">
-        <v>27872.829986741111</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>6.1267584861917072E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
@@ -1983,10 +2154,10 @@
         <v>37</v>
       </c>
       <c r="C34">
-        <v>5876.5</v>
+        <v>9329.2506674511114</v>
       </c>
       <c r="D34">
-        <v>0.99999999999999989</v>
+        <v>5.247298474590243E-2</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
@@ -1997,10 +2168,10 @@
         <v>38</v>
       </c>
       <c r="C35">
-        <v>67452</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
@@ -2011,10 +2182,10 @@
         <v>39</v>
       </c>
       <c r="C36">
-        <v>5388.8934450397901</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0.30397553284426598</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -2067,10 +2238,10 @@
         <v>43</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>37648.51281850152</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>0.5930010949847534</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
@@ -2081,10 +2252,10 @@
         <v>44</v>
       </c>
       <c r="C41">
-        <v>89717</v>
+        <v>3447.5654573478319</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0.28381564947871368</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -2095,10 +2266,10 @@
         <v>45</v>
       </c>
       <c r="C42">
-        <v>18910.09933277778</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0.23549314237581301</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -2123,10 +2294,10 @@
         <v>47</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>11381.10740254888</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>0.180686771578877</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -2137,10 +2308,10 @@
         <v>48</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>6137.3681928279766</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>7.9414299912205374E-2</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
@@ -2151,10 +2322,10 @@
         <v>49</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>112059.5436666465</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>0.95464069776670146</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -2165,10 +2336,10 @@
         <v>50</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>358668.84920827998</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>0.85152026117205193</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
@@ -2179,10 +2350,10 @@
         <v>51</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>60648.99492757181</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>0.33656396584677523</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
@@ -2193,10 +2364,10 @@
         <v>52</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>375739.51248100732</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.89168477471547403</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
@@ -2207,10 +2378,10 @@
         <v>53</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>109878.46954821479</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>0.42343481453823029</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
@@ -2221,10 +2392,10 @@
         <v>54</v>
       </c>
       <c r="C51">
-        <v>54074.75</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
@@ -2235,10 +2406,10 @@
         <v>55</v>
       </c>
       <c r="C52">
-        <v>32030.281558173359</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>0.22793297675270141</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.35">
@@ -2249,10 +2420,10 @@
         <v>56</v>
       </c>
       <c r="C53">
-        <v>7059.1784297499989</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>0.46077157072013109</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.35">
@@ -2263,10 +2434,10 @@
         <v>57</v>
       </c>
       <c r="C54">
-        <v>65256.623933173309</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>0.12715879875518479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.35">
@@ -2277,10 +2448,10 @@
         <v>58</v>
       </c>
       <c r="C55">
-        <v>5533.0294449999983</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>0.22391410311406079</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.35">
@@ -2305,10 +2476,10 @@
         <v>60</v>
       </c>
       <c r="C57">
-        <v>51943.203950019029</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>0.25032567776301018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.35">
@@ -2319,10 +2490,10 @@
         <v>61</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>9664.8465332277556</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>7.4835462221643903E-2</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.35">
@@ -2333,10 +2504,10 @@
         <v>62</v>
       </c>
       <c r="C59">
-        <v>6562.7</v>
+        <v>76759.170119897957</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0.12917634902880751</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.35">
@@ -2347,10 +2518,10 @@
         <v>63</v>
       </c>
       <c r="C60">
-        <v>173427.35646017679</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0.39480136465031063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.35">
@@ -2361,10 +2532,10 @@
         <v>64</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>117384</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.35">
@@ -2403,10 +2574,10 @@
         <v>67</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>10171.07915437571</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>9.9237785918663973E-2</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.35">
@@ -2445,10 +2616,10 @@
         <v>70</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>15121.25441570124</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>0.81391147916684548</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.35">
@@ -2459,10 +2630,10 @@
         <v>71</v>
       </c>
       <c r="C68">
-        <v>48847.186946816502</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0.28126925061650448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.35">
@@ -2473,10 +2644,10 @@
         <v>72</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>13146.39724989796</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2.574519421876283E-2</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.35">
@@ -2487,10 +2658,10 @@
         <v>73</v>
       </c>
       <c r="C70">
-        <v>9681.3372500000005</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>0.64693199131306389</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.35">
@@ -2529,10 +2700,10 @@
         <v>76</v>
       </c>
       <c r="C73">
-        <v>86925.017242212823</v>
+        <v>48003.041250965427</v>
       </c>
       <c r="D73">
-        <v>0.4889154838235395</v>
+        <v>0.85912713293372323</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.35">
@@ -2557,10 +2728,10 @@
         <v>78</v>
       </c>
       <c r="C75">
-        <v>76771.668158745539</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0.15767116748217441</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.35">
@@ -2571,10 +2742,10 @@
         <v>79</v>
       </c>
       <c r="C76">
-        <v>1331.440944999998</v>
+        <v>8931.6695877324019</v>
       </c>
       <c r="D76">
-        <v>5.9466984921288171E-2</v>
+        <v>0.43932365597168788</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.35">
@@ -2599,10 +2770,10 @@
         <v>81</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>5602.6756765704631</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>0.36570171690932468</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.35">
@@ -2627,10 +2798,10 @@
         <v>83</v>
       </c>
       <c r="C80">
-        <v>2327.771732828784</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>3.2958433086669972E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -2641,10 +2812,10 @@
         <v>84</v>
       </c>
       <c r="C81">
-        <v>20313.883992614228</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>0.45543761613824701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -2655,10 +2826,10 @@
         <v>85</v>
       </c>
       <c r="C82">
-        <v>17928.31830270333</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>0.96532594936184957</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -2683,10 +2854,10 @@
         <v>87</v>
       </c>
       <c r="C84">
-        <v>59934.354193269013</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>0.73633950725805031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.35">
@@ -2697,7 +2868,7 @@
         <v>88</v>
       </c>
       <c r="C85">
-        <v>117811.05</v>
+        <v>5110</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -2711,10 +2882,10 @@
         <v>89</v>
       </c>
       <c r="C86">
-        <v>348471.08943452901</v>
+        <v>213298.04048628421</v>
       </c>
       <c r="D86">
-        <v>0.83886768607262796</v>
+        <v>0.41563171629666251</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.35">
@@ -2725,7 +2896,7 @@
         <v>90</v>
       </c>
       <c r="C87">
-        <v>82928</v>
+        <v>123041.5</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -2739,10 +2910,10 @@
         <v>91</v>
       </c>
       <c r="C88">
-        <v>7001.7810427436634</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>5.6905849187011401E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -2753,10 +2924,10 @@
         <v>92</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>1491.8375189927231</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>0.1280459298067706</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -2781,10 +2952,10 @@
         <v>94</v>
       </c>
       <c r="C91">
-        <v>113991.6225534078</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0.1731405973127482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
@@ -2795,10 +2966,10 @@
         <v>95</v>
       </c>
       <c r="C92">
-        <v>73421.697779681344</v>
+        <v>145384.73756664759</v>
       </c>
       <c r="D92">
-        <v>0.58433262178048562</v>
+        <v>0.21540402319858551</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -2809,10 +2980,10 @@
         <v>96</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>14231.35</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.35">
@@ -2865,10 +3036,10 @@
         <v>100</v>
       </c>
       <c r="C97">
-        <v>196321.18058278711</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>0.93374693709011558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.35">
@@ -2879,10 +3050,10 @@
         <v>101</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>163980.03162800669</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>0.37329485718710093</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.35">
@@ -2893,10 +3064,10 @@
         <v>102</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>301054.53646775859</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>0.85596404029341622</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.35">
@@ -2963,10 +3134,10 @@
         <v>107</v>
       </c>
       <c r="C104">
-        <v>71175.195970250003</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>0.58876973703138447</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.35">
@@ -3005,10 +3176,10 @@
         <v>110</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>6778.1013452471088</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>0.34581267545456029</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.35">
@@ -3019,10 +3190,10 @@
         <v>111</v>
       </c>
       <c r="C108">
-        <v>5945.3134687746706</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>0.32382763521744451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.35">
@@ -3033,10 +3204,10 @@
         <v>112</v>
       </c>
       <c r="C109">
-        <v>493972.4954580277</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0.70275640100091408</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.35">
@@ -3047,10 +3218,10 @@
         <v>113</v>
       </c>
       <c r="C110">
-        <v>39080</v>
+        <v>26216.60367714076</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0.15622294601673289</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.35">
@@ -3061,10 +3232,10 @@
         <v>114</v>
       </c>
       <c r="C111">
-        <v>111378</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.35">
@@ -3075,10 +3246,10 @@
         <v>115</v>
       </c>
       <c r="C112">
-        <v>322409.99999999988</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.35">
@@ -3089,10 +3260,10 @@
         <v>116</v>
       </c>
       <c r="C113">
-        <v>425972</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.35">
@@ -3103,10 +3274,10 @@
         <v>117</v>
       </c>
       <c r="C114">
-        <v>155831.5</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.35">
@@ -3117,10 +3288,10 @@
         <v>118</v>
       </c>
       <c r="C115">
-        <v>25402</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.35">
@@ -3131,10 +3302,10 @@
         <v>119</v>
       </c>
       <c r="C116">
-        <v>58978.164462623259</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>0.79429731808736814</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.35">
@@ -3145,10 +3316,10 @@
         <v>120</v>
       </c>
       <c r="C117">
-        <v>60574</v>
+        <v>3613.770355847626</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0.14795375049529691</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.35">
@@ -3159,10 +3330,10 @@
         <v>121</v>
       </c>
       <c r="C118">
-        <v>73275</v>
+        <v>81491.87295725508</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0.1594843405149316</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.35">
@@ -3173,7 +3344,7 @@
         <v>122</v>
       </c>
       <c r="C119">
-        <v>510971</v>
+        <v>155831.5</v>
       </c>
       <c r="D119">
         <v>1</v>
@@ -3187,10 +3358,10 @@
         <v>123</v>
       </c>
       <c r="C120">
-        <v>398886.1359907001</v>
+        <v>60574</v>
       </c>
       <c r="D120">
-        <v>0.60845975467145264</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.35">
@@ -3201,7 +3372,7 @@
         <v>124</v>
       </c>
       <c r="C121">
-        <v>122125</v>
+        <v>304824</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -3215,10 +3386,10 @@
         <v>125</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>25402</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.35">
@@ -3229,10 +3400,10 @@
         <v>126</v>
       </c>
       <c r="C123">
-        <v>60872.292899230029</v>
+        <v>25402</v>
       </c>
       <c r="D123">
-        <v>6.0872298986459931E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.35">
@@ -3243,10 +3414,10 @@
         <v>127</v>
       </c>
       <c r="C124">
-        <v>339902.24394525401</v>
+        <v>207003.15305077279</v>
       </c>
       <c r="D124">
-        <v>3.3990227793548183E-2</v>
+        <v>0.48595483517877408</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.35">
@@ -3257,10 +3428,10 @@
         <v>128</v>
       </c>
       <c r="C125">
-        <v>357577.06388608873</v>
+        <v>7494.6891249999999</v>
       </c>
       <c r="D125">
-        <v>3.5757709964379873E-2</v>
+        <v>0.51140833333333335</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.35">
@@ -3271,10 +3442,10 @@
         <v>129</v>
       </c>
       <c r="C126">
-        <v>766145.02423504461</v>
+        <v>162993.22167908089</v>
       </c>
       <c r="D126">
-        <v>7.661451008495547E-2</v>
+        <v>0.2486293875059008</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.35">
@@ -3285,10 +3456,10 @@
         <v>130</v>
       </c>
       <c r="C127">
-        <v>1579465.226022091</v>
+        <v>322410</v>
       </c>
       <c r="D127">
-        <v>0.1579465383968629</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.35">
@@ -3299,10 +3470,10 @@
         <v>131</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>43774.399641264652</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>0.58953832410257845</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.35">
@@ -3313,10 +3484,10 @@
         <v>132</v>
       </c>
       <c r="C129">
-        <v>1459821.8183171791</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>0.14598219642993759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.35">
@@ -3327,10 +3498,10 @@
         <v>133</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>11669.450833333331</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>0.23888333333333331</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.35">
@@ -3341,10 +3512,10 @@
         <v>134</v>
       </c>
       <c r="C131">
-        <v>999349.7079159728</v>
+        <v>73275</v>
       </c>
       <c r="D131">
-        <v>9.9934980785095356E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.35">
@@ -3355,10 +3526,10 @@
         <v>135</v>
       </c>
       <c r="C132">
-        <v>1123959.1653912279</v>
+        <v>111378</v>
       </c>
       <c r="D132">
-        <v>0.1123959277787156</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.35">
@@ -3369,10 +3540,10 @@
         <v>136</v>
       </c>
       <c r="C133">
-        <v>504093.15183371812</v>
+        <v>36490.417710000002</v>
       </c>
       <c r="D133">
-        <v>5.0409320224303833E-2</v>
+        <v>0.93373637947799393</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.35">
@@ -3383,10 +3554,10 @@
         <v>137</v>
       </c>
       <c r="C134">
-        <v>361199.60244725872</v>
+        <v>28762.640962058911</v>
       </c>
       <c r="D134">
-        <v>3.6119963856722247E-2</v>
+        <v>2.87626438383233E-3</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.35">
@@ -3397,10 +3568,10 @@
         <v>138</v>
       </c>
       <c r="C135">
-        <v>819373.01233299333</v>
+        <v>303112.47827525338</v>
       </c>
       <c r="D135">
-        <v>8.1937309427030272E-2</v>
+        <v>3.031125085865042E-2</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.35">
@@ -3411,10 +3582,10 @@
         <v>139</v>
       </c>
       <c r="C136">
-        <v>139511.8579414433</v>
+        <v>99377.293947232887</v>
       </c>
       <c r="D136">
-        <v>1.395118718926305E-2</v>
+        <v>9.9377303884963276E-3</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.35">
@@ -3425,10 +3596,10 @@
         <v>140</v>
       </c>
       <c r="C137">
-        <v>1536.335261238157</v>
+        <v>1489880.99670054</v>
       </c>
       <c r="D137">
-        <v>1.536335414871698E-4</v>
+        <v>0.14898811456886549</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.35">
@@ -3439,10 +3610,10 @@
         <v>141</v>
       </c>
       <c r="C138">
-        <v>371260</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.35">
@@ -3453,10 +3624,10 @@
         <v>142</v>
       </c>
       <c r="C139">
-        <v>62499.417575951898</v>
+        <v>488874.32838911802</v>
       </c>
       <c r="D139">
-        <v>1.2794148940829459E-2</v>
+        <v>4.8887437727655567E-2</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.35">
@@ -3467,10 +3638,10 @@
         <v>143</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>1036775.174761196</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>0.10367752784387239</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.35">
@@ -3481,10 +3652,10 @@
         <v>144</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>525837.83202316845</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>5.2583788460695689E-2</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.35">
@@ -3495,10 +3666,10 @@
         <v>145</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>737432.8016467616</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>7.3743287539004915E-2</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.35">
@@ -3509,10 +3680,10 @@
         <v>146</v>
       </c>
       <c r="C143">
-        <v>209856.8969753329</v>
+        <v>0</v>
       </c>
       <c r="D143">
-        <v>0.64893423970454245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.35">
@@ -3523,10 +3694,10 @@
         <v>147</v>
       </c>
       <c r="C144">
-        <v>293099.99999999988</v>
+        <v>1318825.7609406009</v>
       </c>
       <c r="D144">
-        <v>1</v>
+        <v>0.131882589282319</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.35">
@@ -3537,10 +3708,10 @@
         <v>148</v>
       </c>
       <c r="C145">
-        <v>255875.51042572121</v>
+        <v>1339214.340100182</v>
       </c>
       <c r="D145">
-        <v>0.72749775510554204</v>
+        <v>0.133921447402163</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.35">
@@ -3551,10 +3722,10 @@
         <v>149</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>764279.93870664702</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>7.6428001513464849E-2</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.35">
@@ -3579,10 +3750,10 @@
         <v>151</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>102483.8928797409</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1.024839031281312E-2</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.35">
@@ -3593,10 +3764,10 @@
         <v>152</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>292335.82209085289</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>2.9233585132443809E-2</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.35">
@@ -3635,10 +3806,10 @@
         <v>155</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>17468.613377422091</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>5.4017673491581583E-2</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.35">
@@ -3691,10 +3862,10 @@
         <v>159</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>305882.06813020923</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>0.86967493497728121</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.35">
@@ -3719,10 +3890,10 @@
         <v>161</v>
       </c>
       <c r="C158">
-        <v>39080</v>
+        <v>371260</v>
       </c>
       <c r="D158">
-        <v>3.908000390800039E-3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.35">
@@ -3733,10 +3904,10 @@
         <v>162</v>
       </c>
       <c r="C159">
-        <v>119643.4077049121</v>
+        <v>293099.99999999988</v>
       </c>
       <c r="D159">
-        <v>1.1964341966925409E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.35">
@@ -3747,10 +3918,10 @@
         <v>163</v>
       </c>
       <c r="C160">
-        <v>320873.66473876173</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>3.2087369682613137E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.35">
@@ -3845,10 +4016,10 @@
         <v>170</v>
       </c>
       <c r="C167">
-        <v>79824.880021608667</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>7.9824888004097466E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.35">
@@ -3943,10 +4114,10 @@
         <v>177</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>111378</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>1.113780111378011E-2</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.35">
@@ -3985,10 +4156,10 @@
         <v>180</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>28762.640962058911</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>2.87626438383233E-3</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.35">
@@ -3999,10 +4170,10 @@
         <v>181</v>
       </c>
       <c r="C178">
-        <v>1536.335261238157</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>1.536335414871698E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.35">
@@ -4013,10 +4184,10 @@
         <v>182</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>60574</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>6.0574006057400607E-3</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.35">
@@ -4111,10 +4282,10 @@
         <v>189</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>1029.2857709887901</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>1.029285873917378E-4</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.35">
@@ -4195,10 +4366,10 @@
         <v>195</v>
       </c>
       <c r="C192">
-        <v>164190.90788846399</v>
+        <v>0</v>
       </c>
       <c r="D192">
-        <v>1.641909243075565E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.35">
@@ -4265,10 +4436,10 @@
         <v>200</v>
       </c>
       <c r="C197">
-        <v>0</v>
+        <v>25402</v>
       </c>
       <c r="D197">
-        <v>0</v>
+        <v>2.5402002540200249E-3</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.35">
@@ -4279,10 +4450,10 @@
         <v>201</v>
       </c>
       <c r="C198">
-        <v>0</v>
+        <v>81491.87295725508</v>
       </c>
       <c r="D198">
-        <v>0</v>
+        <v>8.1491881106443183E-3</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.35">
@@ -4321,10 +4492,10 @@
         <v>204</v>
       </c>
       <c r="C201">
-        <v>425972</v>
+        <v>0</v>
       </c>
       <c r="D201">
-        <v>4.2597204259720432E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.35">
@@ -4349,10 +4520,10 @@
         <v>206</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>203896.55411826479</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>2.0389657450792222E-2</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.35">
@@ -4363,10 +4534,10 @@
         <v>207</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>43774.399641264652</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>4.3774404018705054E-3</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.35">
@@ -4391,10 +4562,10 @@
         <v>209</v>
       </c>
       <c r="C206">
-        <v>339902.24394525401</v>
+        <v>0</v>
       </c>
       <c r="D206">
-        <v>3.3990227793548183E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.35">
@@ -4405,10 +4576,10 @@
         <v>210</v>
       </c>
       <c r="C207">
-        <v>356106.01535984228</v>
+        <v>0</v>
       </c>
       <c r="D207">
-        <v>3.5610605097044737E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.35">
@@ -4615,10 +4786,10 @@
         <v>225</v>
       </c>
       <c r="C222">
-        <v>25402</v>
+        <v>0</v>
       </c>
       <c r="D222">
-        <v>2.5402002540200249E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.35">
@@ -4727,10 +4898,10 @@
         <v>233</v>
       </c>
       <c r="C230">
-        <v>0</v>
+        <v>99377.293947232887</v>
       </c>
       <c r="D230">
-        <v>0</v>
+        <v>9.9377303884963276E-3</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.35">
@@ -4755,10 +4926,10 @@
         <v>235</v>
       </c>
       <c r="C232">
-        <v>0</v>
+        <v>36490.417710000002</v>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>3.649042135904214E-3</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.35">
@@ -4769,10 +4940,10 @@
         <v>236</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>125165.8995882279</v>
       </c>
       <c r="D233">
-        <v>0</v>
+        <v>1.251659121048191E-2</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.35">
@@ -4839,10 +5010,10 @@
         <v>241</v>
       </c>
       <c r="C238">
-        <v>0</v>
+        <v>25402</v>
       </c>
       <c r="D238">
-        <v>0</v>
+        <v>2.5402002540200249E-3</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.35">
@@ -4923,10 +5094,10 @@
         <v>247</v>
       </c>
       <c r="C244">
-        <v>0</v>
+        <v>73275</v>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>7.3275007327500731E-3</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.35">
@@ -4993,10 +5164,10 @@
         <v>252</v>
       </c>
       <c r="C249">
-        <v>53884.577375206951</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>5.388458276366523E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.35">
@@ -5021,10 +5192,10 @@
         <v>254</v>
       </c>
       <c r="C251">
-        <v>60872.292899230029</v>
+        <v>7494.6891249999999</v>
       </c>
       <c r="D251">
-        <v>6.0872298986459931E-3</v>
+        <v>7.4946898744689876E-4</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.35">
@@ -5035,10 +5206,10 @@
         <v>255</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>198733.94019973569</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1.9873396007313169E-2</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.35">
@@ -5063,10 +5234,10 @@
         <v>257</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>303112.47827525338</v>
       </c>
       <c r="D254">
-        <v>0</v>
+        <v>3.031125085865042E-2</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.35">
@@ -5105,10 +5276,10 @@
         <v>260</v>
       </c>
       <c r="C257">
-        <v>0</v>
+        <v>322410</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>3.2241003224100333E-2</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.35">
@@ -5147,10 +5318,10 @@
         <v>263</v>
       </c>
       <c r="C260">
-        <v>1459821.8183171791</v>
+        <v>0</v>
       </c>
       <c r="D260">
-        <v>0.14598219642993751</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.35">
@@ -5161,10 +5332,10 @@
         <v>264</v>
       </c>
       <c r="C261">
-        <v>60574</v>
+        <v>0</v>
       </c>
       <c r="D261">
-        <v>6.0574006057400607E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.35">
@@ -5175,10 +5346,10 @@
         <v>265</v>
       </c>
       <c r="C262">
-        <v>42780.120630857768</v>
+        <v>0</v>
       </c>
       <c r="D262">
-        <v>4.2780124908870258E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.35">
@@ -5189,10 +5360,10 @@
         <v>266</v>
       </c>
       <c r="C263">
-        <v>766145.02423504472</v>
+        <v>0</v>
       </c>
       <c r="D263">
-        <v>7.6614510084955484E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.35">
@@ -5217,10 +5388,10 @@
         <v>268</v>
       </c>
       <c r="C265">
-        <v>0</v>
+        <v>3613.770355847626</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>3.6137707172246978E-4</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.35">
@@ -5371,10 +5542,10 @@
         <v>279</v>
       </c>
       <c r="C276">
-        <v>5093.5870874163083</v>
+        <v>0</v>
       </c>
       <c r="D276">
-        <v>5.0935875967750678E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.35">
@@ -5385,10 +5556,10 @@
         <v>280</v>
       </c>
       <c r="C277">
-        <v>0</v>
+        <v>11669.450833333331</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>1.166945200027853E-3</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.35">
@@ -5525,10 +5696,10 @@
         <v>290</v>
       </c>
       <c r="C287">
-        <v>24754.98766700632</v>
+        <v>0</v>
       </c>
       <c r="D287">
-        <v>2.4754990142505338E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.35">
@@ -5567,10 +5738,10 @@
         <v>293</v>
       </c>
       <c r="C290">
-        <v>0</v>
+        <v>3106.5989325080009</v>
       </c>
       <c r="D290">
-        <v>0</v>
+        <v>3.1065992431679251E-4</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.35">
@@ -5623,10 +5794,10 @@
         <v>297</v>
       </c>
       <c r="C294">
-        <v>113561.275976016</v>
+        <v>0</v>
       </c>
       <c r="D294">
-        <v>1.135612873321447E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.35">
@@ -5665,10 +5836,10 @@
         <v>300</v>
       </c>
       <c r="C297">
-        <v>0</v>
+        <v>737432.8016467616</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>7.3743287539004915E-2</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.35">
@@ -5707,10 +5878,10 @@
         <v>303</v>
       </c>
       <c r="C300">
-        <v>0</v>
+        <v>525837.83202316845</v>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>5.2583788460695689E-2</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.35">
@@ -5735,10 +5906,10 @@
         <v>305</v>
       </c>
       <c r="C302">
-        <v>86623.012332993676</v>
+        <v>0</v>
       </c>
       <c r="D302">
-        <v>8.6623020995295775E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.35">
@@ -5777,10 +5948,10 @@
         <v>308</v>
       </c>
       <c r="C305">
-        <v>73275</v>
+        <v>0</v>
       </c>
       <c r="D305">
-        <v>7.3275007327500731E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.35">
@@ -5791,10 +5962,10 @@
         <v>309</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>764279.93870664702</v>
       </c>
       <c r="D306">
-        <v>0</v>
+        <v>7.6428001513464849E-2</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.35">
@@ -5833,10 +6004,10 @@
         <v>312</v>
       </c>
       <c r="C309">
-        <v>510971</v>
+        <v>0</v>
       </c>
       <c r="D309">
-        <v>5.1097105109710508E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.35">
@@ -5847,10 +6018,10 @@
         <v>313</v>
       </c>
       <c r="C310">
-        <v>155831.5</v>
+        <v>0</v>
       </c>
       <c r="D310">
-        <v>1.558315155831516E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.35">
@@ -5875,10 +6046,10 @@
         <v>315</v>
       </c>
       <c r="C312">
-        <v>122125</v>
+        <v>0</v>
       </c>
       <c r="D312">
-        <v>1.221250122125012E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.35">
@@ -5931,10 +6102,10 @@
         <v>319</v>
       </c>
       <c r="C316">
-        <v>0</v>
+        <v>488874.32838911802</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>4.8887437727655567E-2</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.35">
@@ -5959,10 +6130,10 @@
         <v>321</v>
       </c>
       <c r="C318">
-        <v>555.86415</v>
+        <v>0</v>
       </c>
       <c r="D318">
-        <v>5.5586420558642063E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.35">
@@ -5973,10 +6144,10 @@
         <v>322</v>
       </c>
       <c r="C319">
-        <v>795518.46412499994</v>
+        <v>0</v>
       </c>
       <c r="D319">
-        <v>7.9551854367685429E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.35">
@@ -5987,10 +6158,10 @@
         <v>323</v>
       </c>
       <c r="C320">
-        <v>7561.7455199999986</v>
+        <v>0</v>
       </c>
       <c r="D320">
-        <v>7.5617462761746264E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.35">
@@ -6015,10 +6186,10 @@
         <v>325</v>
       </c>
       <c r="C322">
-        <v>57.643000000000008</v>
+        <v>0</v>
       </c>
       <c r="D322">
-        <v>5.7643005764300594E-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.35">
@@ -6029,10 +6200,10 @@
         <v>326</v>
       </c>
       <c r="C323">
-        <v>2907.0904361571088</v>
+        <v>0</v>
       </c>
       <c r="D323">
-        <v>2.9070907268661822E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.35">
@@ -6043,10 +6214,10 @@
         <v>327</v>
       </c>
       <c r="C324">
-        <v>531.00927000000001</v>
+        <v>0</v>
       </c>
       <c r="D324">
-        <v>5.3100932310093232E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.35">
@@ -6057,10 +6228,10 @@
         <v>328</v>
       </c>
       <c r="C325">
-        <v>8679.5214500000002</v>
+        <v>0</v>
       </c>
       <c r="D325">
-        <v>8.6795223179522317E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.35">
@@ -6071,10 +6242,10 @@
         <v>329</v>
       </c>
       <c r="C326">
-        <v>1915.65275</v>
+        <v>0</v>
       </c>
       <c r="D326">
-        <v>1.9156529415652939E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.35">
@@ -6085,10 +6256,10 @@
         <v>330</v>
       </c>
       <c r="C327">
-        <v>13947.075570000001</v>
+        <v>0</v>
       </c>
       <c r="D327">
-        <v>1.39470769647077E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.35">
@@ -6127,10 +6298,10 @@
         <v>333</v>
       </c>
       <c r="C330">
-        <v>169.49973</v>
+        <v>0</v>
       </c>
       <c r="D330">
-        <v>1.694997469499747E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.35">
@@ -6141,10 +6312,10 @@
         <v>334</v>
       </c>
       <c r="C331">
-        <v>47618.98</v>
+        <v>0</v>
       </c>
       <c r="D331">
-        <v>4.7618984761898476E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.35">
@@ -6155,10 +6326,10 @@
         <v>335</v>
       </c>
       <c r="C332">
-        <v>63.309600000000017</v>
+        <v>0</v>
       </c>
       <c r="D332">
-        <v>6.3309606330960652E-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.35">
@@ -6169,10 +6340,10 @@
         <v>336</v>
       </c>
       <c r="C333">
-        <v>16462.45</v>
+        <v>0</v>
       </c>
       <c r="D333">
-        <v>1.646245164624516E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.35">
@@ -6183,10 +6354,10 @@
         <v>337</v>
       </c>
       <c r="C334">
-        <v>19829.690269999999</v>
+        <v>0</v>
       </c>
       <c r="D334">
-        <v>1.982969225296922E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.35">
@@ -6197,10 +6368,10 @@
         <v>338</v>
       </c>
       <c r="C335">
-        <v>38415.64</v>
+        <v>0</v>
       </c>
       <c r="D335">
-        <v>3.841564384156438E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.35">
@@ -6225,10 +6396,10 @@
         <v>340</v>
       </c>
       <c r="C337">
-        <v>124076.1869468165</v>
+        <v>0</v>
       </c>
       <c r="D337">
-        <v>1.2407619935443639E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.35">
@@ -6281,10 +6452,10 @@
         <v>344</v>
       </c>
       <c r="C341">
-        <v>234149.02171</v>
+        <v>0</v>
       </c>
       <c r="D341">
-        <v>2.341490451249045E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.35">
@@ -6309,10 +6480,10 @@
         <v>346</v>
       </c>
       <c r="C343">
-        <v>1135333.76309</v>
+        <v>0</v>
       </c>
       <c r="D343">
-        <v>0.11353338766233879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.35">
@@ -6323,10 +6494,10 @@
         <v>347</v>
       </c>
       <c r="C344">
-        <v>54642.437599999997</v>
+        <v>299342.37311443489</v>
       </c>
       <c r="D344">
-        <v>5.4642443064244301E-3</v>
+        <v>2.9934240304867521E-2</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.35">
@@ -6351,10 +6522,10 @@
         <v>349</v>
       </c>
       <c r="C346">
-        <v>88096.09</v>
+        <v>0</v>
       </c>
       <c r="D346">
-        <v>8.8096098809609877E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.35">
@@ -6365,10 +6536,10 @@
         <v>350</v>
       </c>
       <c r="C347">
-        <v>6237623.8294370202</v>
+        <v>0</v>
       </c>
       <c r="D347">
-        <v>0.62376244531994651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.35">
@@ -6379,10 +6550,10 @@
         <v>351</v>
       </c>
       <c r="C348">
-        <v>3995.9299999999989</v>
+        <v>155831.5</v>
       </c>
       <c r="D348">
-        <v>3.9959303995930389E-4</v>
+        <v>1.558315155831516E-2</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.35">
@@ -6393,10 +6564,10 @@
         <v>352</v>
       </c>
       <c r="C349">
-        <v>651.66876999999988</v>
+        <v>0</v>
       </c>
       <c r="D349">
-        <v>6.5166883516688337E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.35">
@@ -6407,10 +6578,10 @@
         <v>353</v>
       </c>
       <c r="C350">
-        <v>52.11318</v>
+        <v>0</v>
       </c>
       <c r="D350">
-        <v>5.2113185211318518E-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.35">
@@ -6435,10 +6606,10 @@
         <v>355</v>
       </c>
       <c r="C352">
-        <v>18563</v>
+        <v>0</v>
       </c>
       <c r="D352">
-        <v>1.856300185630018E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.35">
@@ -6449,10 +6620,10 @@
         <v>356</v>
       </c>
       <c r="C353">
-        <v>4274.4726999999993</v>
+        <v>0</v>
       </c>
       <c r="D353">
-        <v>4.2744731274473122E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.35">
@@ -6463,10 +6634,10 @@
         <v>357</v>
       </c>
       <c r="C354">
-        <v>320813.11304000003</v>
+        <v>0</v>
       </c>
       <c r="D354">
-        <v>3.2081314512131448E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.35">
@@ -6477,10 +6648,10 @@
         <v>358</v>
       </c>
       <c r="C355">
-        <v>190671.32</v>
+        <v>37827.322090852947</v>
       </c>
       <c r="D355">
-        <v>1.9067133906713388E-2</v>
+        <v>3.7827325873585529E-3</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.35">
@@ -6491,10 +6662,10 @@
         <v>359</v>
       </c>
       <c r="C356">
-        <v>449.42</v>
+        <v>0</v>
       </c>
       <c r="D356">
-        <v>4.4942004494200447E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.35">
@@ -6505,10 +6676,10 @@
         <v>360</v>
       </c>
       <c r="C357">
-        <v>9035422.2937216479</v>
+        <v>0</v>
       </c>
       <c r="D357">
-        <v>0.90354231972639676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.35">
@@ -6519,10 +6690,10 @@
         <v>361</v>
       </c>
       <c r="C358">
-        <v>1965121.004492735</v>
+        <v>0</v>
       </c>
       <c r="D358">
-        <v>0.19651212010048549</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.35">
@@ -6533,10 +6704,10 @@
         <v>362</v>
       </c>
       <c r="C359">
-        <v>1242293.4195982451</v>
+        <v>304824</v>
       </c>
       <c r="D359">
-        <v>0.12422935438275989</v>
+        <v>3.0482403048240309E-2</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.35">
@@ -6547,10 +6718,10 @@
         <v>363</v>
       </c>
       <c r="C360">
-        <v>287875.63085858681</v>
+        <v>0</v>
       </c>
       <c r="D360">
-        <v>2.8787565964615281E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.35">
@@ -6561,10 +6732,10 @@
         <v>364</v>
       </c>
       <c r="C361">
-        <v>4816654.3745027892</v>
+        <v>0</v>
       </c>
       <c r="D361">
-        <v>0.48166548561682748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.35">
@@ -6575,10 +6746,10 @@
         <v>365</v>
       </c>
       <c r="C362">
-        <v>1709113.3654740441</v>
+        <v>0</v>
       </c>
       <c r="D362">
-        <v>0.17091135363853979</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.35">
@@ -6589,10 +6760,10 @@
         <v>366</v>
       </c>
       <c r="C363">
-        <v>756389.00431332877</v>
+        <v>0</v>
       </c>
       <c r="D363">
-        <v>7.5638907995223673E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.35">
@@ -6603,10 +6774,10 @@
         <v>367</v>
       </c>
       <c r="C364">
-        <v>683.9</v>
+        <v>0</v>
       </c>
       <c r="D364">
-        <v>6.839000683900068E-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.35">
@@ -6617,10 +6788,10 @@
         <v>368</v>
       </c>
       <c r="C365">
-        <v>1412790.1180432269</v>
+        <v>0</v>
       </c>
       <c r="D365">
-        <v>0.1412790259322253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.35">
@@ -6631,10 +6802,10 @@
         <v>369</v>
       </c>
       <c r="C366">
-        <v>1895470.0626843651</v>
+        <v>0</v>
       </c>
       <c r="D366">
-        <v>0.18954702522313899</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.35">
@@ -6659,10 +6830,10 @@
         <v>371</v>
       </c>
       <c r="C368">
-        <v>232141.3214433222</v>
+        <v>0</v>
       </c>
       <c r="D368">
-        <v>2.3214134465745669E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.35">
@@ -6673,10 +6844,10 @@
         <v>372</v>
       </c>
       <c r="C369">
-        <v>1514321.734984355</v>
+        <v>0</v>
       </c>
       <c r="D369">
-        <v>0.15143218864165439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.35">
@@ -6687,10 +6858,10 @@
         <v>373</v>
       </c>
       <c r="C370">
-        <v>1660028.45956802</v>
+        <v>0</v>
       </c>
       <c r="D370">
-        <v>0.16600286255708821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.35">
@@ -6701,10 +6872,10 @@
         <v>374</v>
       </c>
       <c r="C371">
-        <v>571204.75152087398</v>
+        <v>0</v>
       </c>
       <c r="D371">
-        <v>5.7120480864135487E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.35">
@@ -6715,10 +6886,808 @@
         <v>375</v>
       </c>
       <c r="C372">
-        <v>1346210.438308913</v>
+        <v>0</v>
       </c>
       <c r="D372">
-        <v>0.134621057292997</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A373" t="s">
+        <v>4</v>
+      </c>
+      <c r="B373" t="s">
+        <v>376</v>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A374" t="s">
+        <v>4</v>
+      </c>
+      <c r="B374" t="s">
+        <v>377</v>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A375" t="s">
+        <v>4</v>
+      </c>
+      <c r="B375" t="s">
+        <v>378</v>
+      </c>
+      <c r="C375">
+        <v>527.10126999999989</v>
+      </c>
+      <c r="D375">
+        <v>5.2710132271013222E-5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A376" t="s">
+        <v>4</v>
+      </c>
+      <c r="B376" t="s">
+        <v>379</v>
+      </c>
+      <c r="C376">
+        <v>992082.4375</v>
+      </c>
+      <c r="D376">
+        <v>9.9208253670825364E-2</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A377" t="s">
+        <v>4</v>
+      </c>
+      <c r="B377" t="s">
+        <v>380</v>
+      </c>
+      <c r="C377">
+        <v>5354.6634399999994</v>
+      </c>
+      <c r="D377">
+        <v>5.3546639754663966E-4</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A378" t="s">
+        <v>4</v>
+      </c>
+      <c r="B378" t="s">
+        <v>381</v>
+      </c>
+      <c r="C378">
+        <v>0</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A379" t="s">
+        <v>4</v>
+      </c>
+      <c r="B379" t="s">
+        <v>382</v>
+      </c>
+      <c r="C379">
+        <v>146.55000000000001</v>
+      </c>
+      <c r="D379">
+        <v>1.465500146550015E-5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A380" t="s">
+        <v>4</v>
+      </c>
+      <c r="B380" t="s">
+        <v>383</v>
+      </c>
+      <c r="C380">
+        <v>6983.5983716019891</v>
+      </c>
+      <c r="D380">
+        <v>6.9835990699618959E-4</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A381" t="s">
+        <v>4</v>
+      </c>
+      <c r="B381" t="s">
+        <v>384</v>
+      </c>
+      <c r="C381">
+        <v>79.527800000000013</v>
+      </c>
+      <c r="D381">
+        <v>7.9527807952780803E-6</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A382" t="s">
+        <v>4</v>
+      </c>
+      <c r="B382" t="s">
+        <v>385</v>
+      </c>
+      <c r="C382">
+        <v>7367.5569999999998</v>
+      </c>
+      <c r="D382">
+        <v>7.3675577367557734E-4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A383" t="s">
+        <v>4</v>
+      </c>
+      <c r="B383" t="s">
+        <v>386</v>
+      </c>
+      <c r="C383">
+        <v>1821.80213</v>
+      </c>
+      <c r="D383">
+        <v>1.821802312180231E-4</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A384" t="s">
+        <v>4</v>
+      </c>
+      <c r="B384" t="s">
+        <v>387</v>
+      </c>
+      <c r="C384">
+        <v>17600.3619</v>
+      </c>
+      <c r="D384">
+        <v>1.7600363660036371E-3</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A385" t="s">
+        <v>4</v>
+      </c>
+      <c r="B385" t="s">
+        <v>388</v>
+      </c>
+      <c r="C385">
+        <v>0</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A386" t="s">
+        <v>4</v>
+      </c>
+      <c r="B386" t="s">
+        <v>389</v>
+      </c>
+      <c r="C386">
+        <v>0</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A387" t="s">
+        <v>4</v>
+      </c>
+      <c r="B387" t="s">
+        <v>390</v>
+      </c>
+      <c r="C387">
+        <v>120.91352000000001</v>
+      </c>
+      <c r="D387">
+        <v>1.209135320913532E-5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A388" t="s">
+        <v>4</v>
+      </c>
+      <c r="B388" t="s">
+        <v>391</v>
+      </c>
+      <c r="C388">
+        <v>37839.21</v>
+      </c>
+      <c r="D388">
+        <v>3.7839213783921379E-3</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A389" t="s">
+        <v>4</v>
+      </c>
+      <c r="B389" t="s">
+        <v>392</v>
+      </c>
+      <c r="C389">
+        <v>19.452069999999999</v>
+      </c>
+      <c r="D389">
+        <v>1.9452071945207199E-6</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A390" t="s">
+        <v>4</v>
+      </c>
+      <c r="B390" t="s">
+        <v>393</v>
+      </c>
+      <c r="C390">
+        <v>16841.526000000002</v>
+      </c>
+      <c r="D390">
+        <v>1.6841527684152769E-3</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A391" t="s">
+        <v>4</v>
+      </c>
+      <c r="B391" t="s">
+        <v>394</v>
+      </c>
+      <c r="C391">
+        <v>10559.26945</v>
+      </c>
+      <c r="D391">
+        <v>1.0559270505927051E-3</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A392" t="s">
+        <v>4</v>
+      </c>
+      <c r="B392" t="s">
+        <v>395</v>
+      </c>
+      <c r="C392">
+        <v>28726.18388</v>
+      </c>
+      <c r="D392">
+        <v>2.8726186752618681E-3</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A393" t="s">
+        <v>4</v>
+      </c>
+      <c r="B393" t="s">
+        <v>396</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A394" t="s">
+        <v>4</v>
+      </c>
+      <c r="B394" t="s">
+        <v>397</v>
+      </c>
+      <c r="C394">
+        <v>159325.9949275718</v>
+      </c>
+      <c r="D394">
+        <v>1.5932601086017292E-2</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
+        <v>4</v>
+      </c>
+      <c r="B395" t="s">
+        <v>398</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>4</v>
+      </c>
+      <c r="B396" t="s">
+        <v>399</v>
+      </c>
+      <c r="C396">
+        <v>0</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>4</v>
+      </c>
+      <c r="B397" t="s">
+        <v>400</v>
+      </c>
+      <c r="C397">
+        <v>0</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A398" t="s">
+        <v>4</v>
+      </c>
+      <c r="B398" t="s">
+        <v>401</v>
+      </c>
+      <c r="C398">
+        <v>96124.812210000018</v>
+      </c>
+      <c r="D398">
+        <v>9.6124821822482203E-3</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A399" t="s">
+        <v>4</v>
+      </c>
+      <c r="B399" t="s">
+        <v>402</v>
+      </c>
+      <c r="C399">
+        <v>0</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A400" t="s">
+        <v>4</v>
+      </c>
+      <c r="B400" t="s">
+        <v>403</v>
+      </c>
+      <c r="C400">
+        <v>1152595.2818499999</v>
+      </c>
+      <c r="D400">
+        <v>0.115259539710954</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A401" t="s">
+        <v>4</v>
+      </c>
+      <c r="B401" t="s">
+        <v>404</v>
+      </c>
+      <c r="C401">
+        <v>35142.816767503333</v>
+      </c>
+      <c r="D401">
+        <v>3.514282028178536E-3</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A402" t="s">
+        <v>4</v>
+      </c>
+      <c r="B402" t="s">
+        <v>405</v>
+      </c>
+      <c r="C402">
+        <v>0</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A403" t="s">
+        <v>4</v>
+      </c>
+      <c r="B403" t="s">
+        <v>406</v>
+      </c>
+      <c r="C403">
+        <v>91564.439999999988</v>
+      </c>
+      <c r="D403">
+        <v>9.1564449156444905E-3</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A404" t="s">
+        <v>4</v>
+      </c>
+      <c r="B404" t="s">
+        <v>407</v>
+      </c>
+      <c r="C404">
+        <v>5728954.0927535295</v>
+      </c>
+      <c r="D404">
+        <v>0.57289546656489965</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A405" t="s">
+        <v>4</v>
+      </c>
+      <c r="B405" t="s">
+        <v>408</v>
+      </c>
+      <c r="C405">
+        <v>2882.15</v>
+      </c>
+      <c r="D405">
+        <v>2.8821502882150289E-4</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A406" t="s">
+        <v>4</v>
+      </c>
+      <c r="B406" t="s">
+        <v>409</v>
+      </c>
+      <c r="C406">
+        <v>391.16149000000001</v>
+      </c>
+      <c r="D406">
+        <v>3.9116152911615291E-5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A407" t="s">
+        <v>4</v>
+      </c>
+      <c r="B407" t="s">
+        <v>410</v>
+      </c>
+      <c r="C407">
+        <v>37.145539999999997</v>
+      </c>
+      <c r="D407">
+        <v>3.7145543714554371E-6</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A408" t="s">
+        <v>4</v>
+      </c>
+      <c r="B408" t="s">
+        <v>411</v>
+      </c>
+      <c r="C408">
+        <v>0</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A409" t="s">
+        <v>4</v>
+      </c>
+      <c r="B409" t="s">
+        <v>412</v>
+      </c>
+      <c r="C409">
+        <v>18008.063999999998</v>
+      </c>
+      <c r="D409">
+        <v>1.8008065800806581E-3</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A410" t="s">
+        <v>4</v>
+      </c>
+      <c r="B410" t="s">
+        <v>413</v>
+      </c>
+      <c r="C410">
+        <v>22071.504700000001</v>
+      </c>
+      <c r="D410">
+        <v>2.2071506907150691E-3</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A411" t="s">
+        <v>4</v>
+      </c>
+      <c r="B411" t="s">
+        <v>414</v>
+      </c>
+      <c r="C411">
+        <v>336803.22066599998</v>
+      </c>
+      <c r="D411">
+        <v>3.3680325434632542E-2</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A412" t="s">
+        <v>4</v>
+      </c>
+      <c r="B412" t="s">
+        <v>415</v>
+      </c>
+      <c r="C412">
+        <v>172908.3456243854</v>
+      </c>
+      <c r="D412">
+        <v>1.7290836291522171E-2</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A413" t="s">
+        <v>4</v>
+      </c>
+      <c r="B413" t="s">
+        <v>416</v>
+      </c>
+      <c r="C413">
+        <v>209.71305000000001</v>
+      </c>
+      <c r="D413">
+        <v>2.0971307097130711E-5</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A414" t="s">
+        <v>4</v>
+      </c>
+      <c r="B414" t="s">
+        <v>417</v>
+      </c>
+      <c r="C414">
+        <v>9999999</v>
+      </c>
+      <c r="D414">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A415" t="s">
+        <v>4</v>
+      </c>
+      <c r="B415" t="s">
+        <v>418</v>
+      </c>
+      <c r="C415">
+        <v>2132790.764230879</v>
+      </c>
+      <c r="D415">
+        <v>0.21327909775099771</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A416" t="s">
+        <v>4</v>
+      </c>
+      <c r="B416" t="s">
+        <v>419</v>
+      </c>
+      <c r="C416">
+        <v>1338762.3107718481</v>
+      </c>
+      <c r="D416">
+        <v>0.13387624446480931</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A417" t="s">
+        <v>4</v>
+      </c>
+      <c r="B417" t="s">
+        <v>420</v>
+      </c>
+      <c r="C417">
+        <v>244187.53104004939</v>
+      </c>
+      <c r="D417">
+        <v>2.441875554588049E-2</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A418" t="s">
+        <v>4</v>
+      </c>
+      <c r="B418" t="s">
+        <v>421</v>
+      </c>
+      <c r="C418">
+        <v>5194976.9121760055</v>
+      </c>
+      <c r="D418">
+        <v>0.51949774316737485</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A419" t="s">
+        <v>4</v>
+      </c>
+      <c r="B419" t="s">
+        <v>422</v>
+      </c>
+      <c r="C419">
+        <v>1768141.250753962</v>
+      </c>
+      <c r="D419">
+        <v>0.17681414275681051</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A420" t="s">
+        <v>4</v>
+      </c>
+      <c r="B420" t="s">
+        <v>423</v>
+      </c>
+      <c r="C420">
+        <v>750869.22871639486</v>
+      </c>
+      <c r="D420">
+        <v>7.5086930380332526E-2</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A421" t="s">
+        <v>4</v>
+      </c>
+      <c r="B421" t="s">
+        <v>424</v>
+      </c>
+      <c r="C421">
+        <v>683.9</v>
+      </c>
+      <c r="D421">
+        <v>6.839000683900068E-5</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A422" t="s">
+        <v>4</v>
+      </c>
+      <c r="B422" t="s">
+        <v>425</v>
+      </c>
+      <c r="C422">
+        <v>1129419.8863680379</v>
+      </c>
+      <c r="D422">
+        <v>0.1129419999310038</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A423" t="s">
+        <v>4</v>
+      </c>
+      <c r="B423" t="s">
+        <v>426</v>
+      </c>
+      <c r="C423">
+        <v>2288704.1568338252</v>
+      </c>
+      <c r="D423">
+        <v>0.22887043857042641</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A424" t="s">
+        <v>4</v>
+      </c>
+      <c r="B424" t="s">
+        <v>427</v>
+      </c>
+      <c r="C424">
+        <v>0</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A425" t="s">
+        <v>4</v>
+      </c>
+      <c r="B425" t="s">
+        <v>428</v>
+      </c>
+      <c r="C425">
+        <v>308590.22299160768</v>
+      </c>
+      <c r="D425">
+        <v>3.0859025385063309E-2</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A426" t="s">
+        <v>4</v>
+      </c>
+      <c r="B426" t="s">
+        <v>429</v>
+      </c>
+      <c r="C426">
+        <v>1259517.180291699</v>
+      </c>
+      <c r="D426">
+        <v>0.12595173062434301</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A427" t="s">
+        <v>4</v>
+      </c>
+      <c r="B427" t="s">
+        <v>430</v>
+      </c>
+      <c r="C427">
+        <v>1828659.302226193</v>
+      </c>
+      <c r="D427">
+        <v>0.18286594850921409</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A428" t="s">
+        <v>4</v>
+      </c>
+      <c r="B428" t="s">
+        <v>431</v>
+      </c>
+      <c r="C428">
+        <v>557871.03573034669</v>
+      </c>
+      <c r="D428">
+        <v>5.5787109151745583E-2</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A429" t="s">
+        <v>4</v>
+      </c>
+      <c r="B429" t="s">
+        <v>432</v>
+      </c>
+      <c r="C429">
+        <v>1419953.943201544</v>
+      </c>
+      <c r="D429">
+        <v>0.14199540851969519</v>
       </c>
     </row>
   </sheetData>

--- a/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/01_raw_results/outputs_IAEE_2025_run_2021.xlsx
+++ b/01_data/02_output_data/02_unidirectional_results/01_paper_IAEE/01_raw_results/outputs_IAEE_2025_run_2021.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D429"/>
+  <dimension ref="A1:D372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,7 +458,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>('UA', 'PL')</t>
+          <t>('DE', 'LU')</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -476,7 +476,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>('LT', 'LV')</t>
+          <t>('DZ', 'ES')</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -494,14 +494,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>('DE', 'AT')</t>
+          <t>('UA', 'MD')</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>109878.4695482148</v>
+        <v>1117.368709865174</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4234348145382303</v>
+        <v>0.01198339642314117</v>
       </c>
     </row>
     <row r="5">
@@ -512,14 +512,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>('NO', 'DE')</t>
+          <t>('DK', 'DE')</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>447490</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -530,14 +530,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>('RU', 'BY')</t>
+          <t>('MD', 'RO')</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>163980.0316280067</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3732948571871009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -548,14 +548,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>('HU', 'HR')</t>
+          <t>('DZ', 'TN')</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>364986.8167072563</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.8786256755906718</v>
       </c>
     </row>
     <row r="8">
@@ -566,14 +566,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>('SK', 'AT')</t>
+          <t>('DE', 'PL')</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>85227.5</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>('DE', 'LU')</t>
+          <t>('BE', 'FR')</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -602,14 +602,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>('RS', 'BA')</t>
+          <t>('RU', 'LV')</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5110</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>('IT', 'AT')</t>
+          <t>('EE', 'LV')</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -638,14 +638,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>('BE', 'DE')</t>
+          <t>('LT', 'LV')</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>16018.07132</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.649188267812272</v>
       </c>
     </row>
     <row r="13">
@@ -656,14 +656,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>('NL', 'UK')</t>
+          <t>('NO', 'NL')</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>351714</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -674,14 +674,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>('PL', 'SK')</t>
+          <t>('DE', 'DK')</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37648.51281850152</v>
+        <v>18425.94820709651</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5930010949847534</v>
+        <v>0.3708861076353018</v>
       </c>
     </row>
     <row r="15">
@@ -692,14 +692,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>('UK', 'IE')</t>
+          <t>('FR', 'ES')</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>11163.69681353934</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07944278109617037</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -710,7 +710,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>('FR', 'DE')</t>
+          <t>('RO', 'BG')</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -728,14 +728,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>('UA', 'HU')</t>
+          <t>('BG', 'MK')</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>3174.72765343728</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>0.3176728992702683</v>
       </c>
     </row>
     <row r="18">
@@ -746,7 +746,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>('BY', 'PL')</t>
+          <t>('RU', 'DE')</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -764,14 +764,14 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>('BG', 'RO')</t>
+          <t>('BY', 'PL')</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6137.368192827977</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.07941429991220537</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -782,14 +782,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>('DZ', 'MA')</t>
+          <t>('ES', 'FR')</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1491.837518992723</v>
+        <v>81906</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1280459298067706</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -800,14 +800,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>('TN', 'IT')</t>
+          <t>('NO', 'DE')</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>358668.84920828</v>
+        <v>455155</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8515202611720519</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -818,14 +818,14 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>('PT', 'ES')</t>
+          <t>('TR', 'EL')</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>75554.49584221284</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.5240471360652876</v>
       </c>
     </row>
     <row r="23">
@@ -836,14 +836,14 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>('DE', 'FR')</t>
+          <t>('CH', 'DE')</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>27549.51808215789</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.4367947438190939</v>
       </c>
     </row>
     <row r="24">
@@ -854,14 +854,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>('NO', 'NL')</t>
+          <t>('BG', 'RS')</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>301054.5364677586</v>
+        <v>111067.9616993498</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8559640402934162</v>
+        <v>0.7643126252170662</v>
       </c>
     </row>
     <row r="25">
@@ -872,14 +872,14 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>('PL', 'DE')</t>
+          <t>('CZ', 'PL')</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>5357.041566666689</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.5241723646444901</v>
       </c>
     </row>
     <row r="26">
@@ -890,14 +890,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>('DE', 'DK')</t>
+          <t>('IT', 'SI')</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>8302.805820583826</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>0.7981548493711921</v>
       </c>
     </row>
     <row r="27">
@@ -908,14 +908,14 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>('DE', 'CH')</t>
+          <t>('AL', 'IT')</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>9664.846533227756</v>
+        <v>79762.94794968615</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0748354622216439</v>
+        <v>0.4486319534380785</v>
       </c>
     </row>
     <row r="28">
@@ -926,14 +926,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>('DK', 'DE')</t>
+          <t>('NO', 'BE')</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>167754</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -944,14 +944,14 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>('DE', 'CZ')</t>
+          <t>('PL', 'DE')</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>76759.17011989796</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1291763490288075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -962,7 +962,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>('DE', 'PL')</t>
+          <t>('NL', 'BE')</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -980,14 +980,14 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>('LU', 'BE')</t>
+          <t>('CZ', 'SK')</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>27872.82998674111</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>0.06126758486191707</v>
       </c>
     </row>
     <row r="32">
@@ -998,7 +998,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>('SK', 'CZ')</t>
+          <t>('BE', 'UK')</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>('SK', 'PL')</t>
+          <t>('AT', 'IT')</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1034,14 +1034,14 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>('CH', 'DE')</t>
+          <t>('RO', 'MD')</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>5876.5</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>0.9999999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1052,14 +1052,14 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>('IT', 'CH')</t>
+          <t>('UK', 'NL')</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17145.23318528819</v>
+        <v>67452</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1211118772812409</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1070,14 +1070,14 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>('FI', 'EE')</t>
+          <t>('HR', 'HU')</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>5388.89344503979</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>0.303975532844266</v>
       </c>
     </row>
     <row r="37">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>('CZ', 'PL')</t>
+          <t>('FR', 'BE')</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>('RU', 'LV')</t>
+          <t>('ES', 'PT')</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1124,14 +1124,14 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>('BG', 'RS')</t>
+          <t>('DE', 'NL')</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>26216.60367714076</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1562229460167329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>('BG', 'TR')</t>
+          <t>('AT', 'HU')</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1160,14 +1160,14 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>('EE', 'LV')</t>
+          <t>('RS', 'HU')</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>89717</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -1178,14 +1178,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>('HU', 'SK')</t>
+          <t>('RU', 'FI')</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>18910.09933277778</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>0.235493142375813</v>
       </c>
     </row>
     <row r="43">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>('NO', 'UK')</t>
+          <t>('BY', 'LT')</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>213298.0404862842</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.4156317162966625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1214,14 +1214,14 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>('DZ', 'ES')</t>
+          <t>('SI', 'IT')</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>123041.5</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>('DE', 'BE')</t>
+          <t>('BG', 'TR')</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>('RS', 'HU')</t>
+          <t>('SK', 'AT')</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>('ES', 'FR')</t>
+          <t>('BG', 'EL')</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>('BE', 'UK')</t>
+          <t>('LV', 'RU')</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>('SK', 'HU')</t>
+          <t>('MD', 'UA')</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -1322,14 +1322,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>('DK', 'SE')</t>
+          <t>('EL', 'BG')</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>6997.265946547327</v>
+        <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.6390197211458746</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1340,14 +1340,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>('HR', 'SI')</t>
+          <t>('BG', 'RO')</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>54074.75</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -1358,14 +1358,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>('RO', 'HU')</t>
+          <t>('UK', 'IE')</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>32030.28155817336</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>0.2279329767527014</v>
       </c>
     </row>
     <row r="53">
@@ -1376,14 +1376,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>('UA', 'SK')</t>
+          <t>('BE', 'LU')</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>7059.178429749999</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.4607715707201311</v>
       </c>
     </row>
     <row r="54">
@@ -1394,14 +1394,14 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>('BG', 'EL')</t>
+          <t>('NO', 'UK')</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>65256.62393317331</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>0.1271587987551848</v>
       </c>
     </row>
     <row r="55">
@@ -1412,14 +1412,14 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>('EL', 'BG')</t>
+          <t>('LV', 'EE')</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>11381.10740254888</v>
+        <v>5533.029444999998</v>
       </c>
       <c r="D55" t="n">
-        <v>0.180686771578877</v>
+        <v>0.2239141031140608</v>
       </c>
     </row>
     <row r="56">
@@ -1430,14 +1430,14 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>('SI', 'HR')</t>
+          <t>('NL', 'UK')</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6778.101345247109</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.3458126754545603</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>('CH', 'IT')</t>
+          <t>('NO', 'FR')</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>51943.20395001903</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>0.2503256777630102</v>
       </c>
     </row>
     <row r="58">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>('UA', 'MD')</t>
+          <t>('DE', 'BE')</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1484,14 +1484,14 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>('CZ', 'SK')</t>
+          <t>('RS', 'BA')</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>13146.39724989796</v>
+        <v>6562.7</v>
       </c>
       <c r="D59" t="n">
-        <v>0.02574519421876283</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -1502,14 +1502,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>('RU', 'DE')</t>
+          <t>('RU', 'BY')</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0</v>
+        <v>173427.3564601768</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
+        <v>0.3948013646503106</v>
       </c>
     </row>
     <row r="61">
@@ -1520,14 +1520,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>('RO', 'MD')</t>
+          <t>('CH', 'FR')</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8931.669587732402</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.4393236559716879</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>('LV', 'EE')</t>
+          <t>('HU', 'RS')</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>('BE', 'NL')</t>
+          <t>('MA', 'ES')</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>('NL', 'BE')</t>
+          <t>('CH', 'IT')</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -1592,14 +1592,14 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>('AT', 'HU')</t>
+          <t>('AT', 'SK')</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>48003.04125096543</v>
+        <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0.8591271329337232</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>('HU', 'RO')</t>
+          <t>('LT', 'RU')</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>('AT', 'SK')</t>
+          <t>('RS', 'BG')</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -1646,14 +1646,14 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>('IT', 'SI')</t>
+          <t>('LY', 'IT')</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>14231.35</v>
+        <v>48847.1869468165</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>0.2812692506165045</v>
       </c>
     </row>
     <row r="69">
@@ -1664,14 +1664,14 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>('LY', 'IT')</t>
+          <t>('PT', 'ES')</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>60648.99492757181</v>
+        <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.3365639658467752</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1682,14 +1682,14 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>('MD', 'RO')</t>
+          <t>('DK', 'SE')</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0</v>
+        <v>9681.33725</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
+        <v>0.6469319913130639</v>
       </c>
     </row>
     <row r="71">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>('UA', 'RO')</t>
+          <t>('CZ', 'DE')</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>('DE', 'NL')</t>
+          <t>('SK', 'UA')</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -1736,14 +1736,14 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>('AT', 'DE')</t>
+          <t>('EL', 'AL')</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>86925.01724221282</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
+        <v>0.4889154838235395</v>
       </c>
     </row>
     <row r="74">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>('UK', 'BE')</t>
+          <t>('AT', 'DE')</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -1772,14 +1772,14 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>('BE', 'LU')</t>
+          <t>('RU', 'UA')</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>5602.675676570463</v>
+        <v>76771.66815874554</v>
       </c>
       <c r="D75" t="n">
-        <v>0.3657017169093247</v>
+        <v>0.1576711674821744</v>
       </c>
     </row>
     <row r="76">
@@ -1790,14 +1790,14 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>('TR', 'BG')</t>
+          <t>('EE', 'FI')</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>49019.92212476768</v>
+        <v>1331.440944999998</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2331495868378606</v>
+        <v>0.05946698492128817</v>
       </c>
     </row>
     <row r="77">
@@ -1808,14 +1808,14 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>('NL', 'DE')</t>
+          <t>('UA', 'PL')</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>145384.7375666476</v>
+        <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2154040231985855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>('MA', 'ES')</t>
+          <t>('FI', 'EE')</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -1844,14 +1844,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>('BG', 'MK')</t>
+          <t>('SK', 'CZ')</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>3447.565457347832</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2838156494787137</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1862,14 +1862,14 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>('NO', 'FR')</t>
+          <t>('IT', 'AT')</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8321.95294038061</v>
+        <v>2327.771732828784</v>
       </c>
       <c r="D80" t="n">
-        <v>0.04010531410648358</v>
+        <v>0.03295843308666997</v>
       </c>
     </row>
     <row r="81">
@@ -1880,14 +1880,14 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>('AT', 'SI')</t>
+          <t>('RO', 'UA')</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>20313.88399261423</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>0.455437616138247</v>
       </c>
     </row>
     <row r="82">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>('HU', 'RS')</t>
+          <t>('HU', 'SK')</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>0</v>
+        <v>17928.31830270333</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>0.9653259493618496</v>
       </c>
     </row>
     <row r="83">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>('FR', 'BE')</t>
+          <t>('HR', 'SI')</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -1934,14 +1934,14 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>('FR', 'ES')</t>
+          <t>('FR', 'CH')</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>59934.35419326901</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
+        <v>0.7363395072580503</v>
       </c>
     </row>
     <row r="85">
@@ -1952,11 +1952,11 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>('NO', 'DK')</t>
+          <t>('BE', 'DE')</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>117384</v>
+        <v>117811.05</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -1970,14 +1970,14 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>('ES', 'PT')</t>
+          <t>('TN', 'IT')</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>348471.089434529</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>0.838867686072628</v>
       </c>
     </row>
     <row r="87">
@@ -1988,14 +1988,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>('RU', 'TR')</t>
+          <t>('UK', 'BE')</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>0</v>
+        <v>82928</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -2006,14 +2006,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>('BE', 'FR')</t>
+          <t>('DZ', 'MA')</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>0</v>
+        <v>7001.781042743663</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
+        <v>0.0569058491870114</v>
       </c>
     </row>
     <row r="89">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>('BY', 'UA')</t>
+          <t>('AT', 'SI')</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>('TR', 'EL')</t>
+          <t>('UA', 'SK')</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -2060,14 +2060,14 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>('RS', 'BG')</t>
+          <t>('DE', 'CZ')</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>0</v>
+        <v>113991.6225534078</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>0.1731405973127482</v>
       </c>
     </row>
     <row r="92">
@@ -2078,14 +2078,14 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>('AL', 'IT')</t>
+          <t>('DE', 'AT')</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>73421.69777968134</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>0.5843326217804856</v>
       </c>
     </row>
     <row r="93">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>('CZ', 'DE')</t>
+          <t>('IT', 'CH')</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>('RO', 'BG')</t>
+          <t>('DE', 'FR')</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>('AT', 'IT')</t>
+          <t>('BY', 'UA')</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>('RU', 'FI')</t>
+          <t>('HU', 'RO')</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -2168,14 +2168,14 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>('BY', 'LT')</t>
+          <t>('TR', 'BG')</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>196321.1805827871</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
+        <v>0.9337469370901156</v>
       </c>
     </row>
     <row r="98">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>('EE', 'FI')</t>
+          <t>('SK', 'HU')</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>('RU', 'UA')</t>
+          <t>('UA', 'HU')</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -2222,14 +2222,14 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>('DK', 'PL')</t>
+          <t>('LV', 'LT')</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>112059.5436666465</v>
+        <v>0</v>
       </c>
       <c r="D100" t="n">
-        <v>0.9546406977667015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>('FR', 'CH')</t>
+          <t>('LU', 'BE')</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>('MD', 'UA')</t>
+          <t>('DE', 'CH')</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>('LT', 'RU')</t>
+          <t>('RU', 'TR')</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -2294,14 +2294,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>('SK', 'UA')</t>
+          <t>('BE', 'NL')</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10171.07915437571</v>
+        <v>71175.19597025</v>
       </c>
       <c r="D104" t="n">
-        <v>0.09923778591866397</v>
+        <v>0.5887697370313845</v>
       </c>
     </row>
     <row r="105">
@@ -2312,14 +2312,14 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>('NO', 'BE')</t>
+          <t>('UA', 'RO')</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>27987.08721461517</v>
+        <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.16919009548305</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2330,14 +2330,14 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>('LT', 'PL')</t>
+          <t>('SI', 'HR')</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>21195.258</v>
+        <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>('RO', 'UA')</t>
+          <t>('HU', 'HR')</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>('LV', 'LT')</t>
+          <t>('RO', 'HU')</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0</v>
+        <v>5945.313468774671</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
+        <v>0.3238276352174445</v>
       </c>
     </row>
     <row r="109">
@@ -2384,14 +2384,14 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>('UK', 'NL')</t>
+          <t>('NL', 'DE')</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>0</v>
+        <v>493972.4954580277</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>0.7027564010009141</v>
       </c>
     </row>
     <row r="110">
@@ -2402,14 +2402,14 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>('EL', 'AL')</t>
+          <t>('LT_LNG_imp', 'LT')</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>9329.250667451111</v>
+        <v>39080</v>
       </c>
       <c r="D110" t="n">
-        <v>0.05247298474590243</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
@@ -2420,14 +2420,14 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>('PL', 'DK')</t>
+          <t>('BE_LNG_imp', 'BE')</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>111378</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
@@ -2438,14 +2438,14 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>('LV', 'RU')</t>
+          <t>('FR_LNG_imp', 'FR')</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>322409.9999999999</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>('CH', 'FR')</t>
+          <t>('TR_LNG_imp', 'TR')</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>425972</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -2474,14 +2474,14 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>('DZ', 'TN')</t>
+          <t>('IT_LNG_imp', 'IT')</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>375739.5124810073</v>
+        <v>155831.5</v>
       </c>
       <c r="D114" t="n">
-        <v>0.891684774715474</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -2492,14 +2492,14 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>('SI', 'IT')</t>
+          <t>('HR_LNG_imp', 'HR')</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>0</v>
+        <v>25402</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -2510,14 +2510,14 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>('HR', 'HU')</t>
+          <t>('PT_LNG_imp', 'PT')</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>15121.25441570124</v>
+        <v>58978.16446262326</v>
       </c>
       <c r="D116" t="n">
-        <v>0.8139114791668455</v>
+        <v>0.7942973180873681</v>
       </c>
     </row>
     <row r="117">
@@ -2528,14 +2528,14 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>('NL_LNG_imp', 'NL')</t>
+          <t>('PL_LNG_imp', 'PL')</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>60574</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -2546,14 +2546,14 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>('ES_LNG_imp', 'ES')</t>
+          <t>('EL_LNG_imp', 'EL')</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>162993.2216790809</v>
+        <v>73275</v>
       </c>
       <c r="D118" t="n">
-        <v>0.2486293875059008</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
@@ -2564,14 +2564,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>('TR_LNG_imp', 'TR')</t>
+          <t>('UK_LNG_imp', 'UK')</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>207003.1530507728</v>
+        <v>510971</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4859548351787741</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
@@ -2582,14 +2582,14 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>('IT_LNG_imp', 'IT')</t>
+          <t>('ES_LNG_imp', 'ES')</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>155831.5</v>
+        <v>398886.1359907001</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>0.6084597546714526</v>
       </c>
     </row>
     <row r="121">
@@ -2600,11 +2600,11 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>('IE_LNG_imp', 'IE')</t>
+          <t>('NL_LNG_imp', 'NL')</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>25402</v>
+        <v>122125</v>
       </c>
       <c r="D121" t="n">
         <v>1</v>
@@ -2618,14 +2618,14 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>('BE_LNG_imp', 'BE')</t>
+          <t>('EG_LNG_imp', 'EG')</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>111378</v>
+        <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2636,14 +2636,14 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>('EE_LNG_imp', 'EE')</t>
+          <t>('SA_LNG_imp', 'SA')</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>3613.770355847626</v>
+        <v>60872.29289923003</v>
       </c>
       <c r="D123" t="n">
-        <v>0.1479537504952969</v>
+        <v>0.006087229898645993</v>
       </c>
     </row>
     <row r="124">
@@ -2654,14 +2654,14 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>('PL_LNG_imp', 'PL')</t>
+          <t>('AS_LNG_imp', 'AS')</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>60574</v>
+        <v>339902.243945254</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>0.03399022779354818</v>
       </c>
     </row>
     <row r="125">
@@ -2672,14 +2672,14 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>('LV_LNG_imp', 'LV')</t>
+          <t>('IN_LNG_imp', 'IN')</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>7494.689125</v>
+        <v>357577.0638860887</v>
       </c>
       <c r="D125" t="n">
-        <v>0.5114083333333334</v>
+        <v>0.03575770996437987</v>
       </c>
     </row>
     <row r="126">
@@ -2690,14 +2690,14 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>('HR_LNG_imp', 'HR')</t>
+          <t>('CN_LNG_imp', 'CN')</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>25402</v>
+        <v>766145.0242350446</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>0.07661451008495547</v>
       </c>
     </row>
     <row r="127">
@@ -2708,14 +2708,14 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>('EL_LNG_imp', 'EL')</t>
+          <t>('JS_LNG_imp', 'JS')</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>73275</v>
+        <v>1579465.226022091</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>0.1579465383968629</v>
       </c>
     </row>
     <row r="128">
@@ -2726,14 +2726,14 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>('UK_LNG_imp', 'UK')</t>
+          <t>('AF_LNG_imp', 'AF')</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>81491.87295725508</v>
+        <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.1594843405149316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2744,14 +2744,14 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>('FI_LNG_imp', 'FI')</t>
+          <t>('RU', 'RU_LNG_exp')</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>11669.45083333333</v>
+        <v>1459821.818317179</v>
       </c>
       <c r="D129" t="n">
-        <v>0.2388833333333333</v>
+        <v>0.1459821964299376</v>
       </c>
     </row>
     <row r="130">
@@ -2762,14 +2762,14 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>('PT_LNG_imp', 'PT')</t>
+          <t>('ME', 'ME_LNG_exp')</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>43774.39964126465</v>
+        <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.5895383241025784</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -2780,14 +2780,14 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>('LT_LNG_imp', 'LT')</t>
+          <t>('AU', 'AU_LNG_exp')</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>36490.41771</v>
+        <v>999349.7079159728</v>
       </c>
       <c r="D131" t="n">
-        <v>0.9337363794779939</v>
+        <v>0.09993498078509536</v>
       </c>
     </row>
     <row r="132">
@@ -2798,14 +2798,14 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>('FR_LNG_imp', 'FR')</t>
+          <t>('QA', 'QA_LNG_exp')</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>322409.9999999999</v>
+        <v>1123959.165391228</v>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>0.1123959277787156</v>
       </c>
     </row>
     <row r="133">
@@ -2816,14 +2816,14 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>('DE_LNG_imp', 'DE')</t>
+          <t>('IM', 'IM_LNG_exp')</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>304823.9999999999</v>
+        <v>504093.1518337181</v>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>0.05040932022430383</v>
       </c>
     </row>
     <row r="134">
@@ -2834,14 +2834,14 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>('JS_LNG_imp', 'JS')</t>
+          <t>('AF', 'AF_LNG_exp')</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>1489880.99670054</v>
+        <v>361199.6024472587</v>
       </c>
       <c r="D134" t="n">
-        <v>0.1489881145688655</v>
+        <v>0.03611996385672225</v>
       </c>
     </row>
     <row r="135">
@@ -2852,14 +2852,14 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>('CN_LNG_imp', 'CN')</t>
+          <t>('USA', 'USA_LNG_exp')</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>1036775.174761196</v>
+        <v>819373.0123329933</v>
       </c>
       <c r="D135" t="n">
-        <v>0.1036775278438724</v>
+        <v>0.08193730942703027</v>
       </c>
     </row>
     <row r="136">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>('AF_LNG_imp', 'AF')</t>
+          <t>('TT', 'TT_LNG_exp')</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>0</v>
+        <v>139511.8579414433</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>0.01395118718926305</v>
       </c>
     </row>
     <row r="137">
@@ -2888,14 +2888,14 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>('IN_LNG_imp', 'IN')</t>
+          <t>('EG', 'EG_LNG_exp')</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>303112.4782752534</v>
+        <v>1536.335261238157</v>
       </c>
       <c r="D137" t="n">
-        <v>0.03031125085865042</v>
+        <v>0.0001536335414871698</v>
       </c>
     </row>
     <row r="138">
@@ -2906,14 +2906,14 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>('EG_LNG_imp', 'EG')</t>
+          <t>('RU', 'CN')</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>28762.64096205891</v>
+        <v>371260</v>
       </c>
       <c r="D138" t="n">
-        <v>0.00287626438383233</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
@@ -2924,14 +2924,14 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>('AS_LNG_imp', 'AS')</t>
+          <t>('USA', 'CM')</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>488874.328389118</v>
+        <v>62499.4175759519</v>
       </c>
       <c r="D139" t="n">
-        <v>0.04888743772765557</v>
+        <v>0.01279414894082946</v>
       </c>
     </row>
     <row r="140">
@@ -2942,14 +2942,14 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>('SA_LNG_imp', 'SA')</t>
+          <t>('ME', 'QA')</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>99377.29394723289</v>
+        <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.009937730388496328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -2960,14 +2960,14 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>('TT', 'TT_LNG_exp')</t>
+          <t>('ME', 'CR')</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>102483.8928797409</v>
+        <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.01024839031281312</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -2978,14 +2978,14 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>('QA', 'QA_LNG_exp')</t>
+          <t>('AS', 'CN')</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>1318825.760940601</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.131882589282319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -2996,14 +2996,14 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>('USA', 'USA_LNG_exp')</t>
+          <t>('QA', 'ME')</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>1339214.340100182</v>
+        <v>209856.8969753329</v>
       </c>
       <c r="D143" t="n">
-        <v>0.133921447402163</v>
+        <v>0.6489342397045424</v>
       </c>
     </row>
     <row r="144">
@@ -3014,14 +3014,14 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>('ME', 'ME_LNG_exp')</t>
+          <t>('CR', 'TR')</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0</v>
+        <v>293099.9999999999</v>
       </c>
       <c r="D144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -3032,14 +3032,14 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>('AF', 'AF_LNG_exp')</t>
+          <t>('CR', 'CN')</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>292335.8220908529</v>
+        <v>255875.5104257212</v>
       </c>
       <c r="D145" t="n">
-        <v>0.02923358513244381</v>
+        <v>0.727497755105542</v>
       </c>
     </row>
     <row r="146">
@@ -3050,14 +3050,14 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>('AU', 'AU_LNG_exp')</t>
+          <t>('ME', 'AF')</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>737432.8016467615</v>
+        <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.0737432875390049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -3068,14 +3068,14 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>('RU', 'RU_LNG_exp')</t>
+          <t>('CM', 'USA')</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>764279.938706647</v>
+        <v>0</v>
       </c>
       <c r="D147" t="n">
-        <v>0.07642800151346485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>('IM', 'IM_LNG_exp')</t>
+          <t>('RU', 'CR')</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>525837.8320231684</v>
+        <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.05258378846069569</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>('EG', 'EG_LNG_exp')</t>
+          <t>('QA_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -3122,14 +3122,14 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>('QA', 'ME')</t>
+          <t>('AF_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>17468.61337742209</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.05401767349158158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>('ME', 'AF')</t>
+          <t>('AF_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -3158,14 +3158,14 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>('CR', 'CN')</t>
+          <t>('RU_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>305882.0681302092</v>
+        <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.8696749349772812</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>('AS', 'CN')</t>
+          <t>('EG_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -3194,14 +3194,14 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>('CR', 'TR')</t>
+          <t>('IM_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>293099.9999999999</v>
+        <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
@@ -3212,14 +3212,14 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>('RU', 'CN')</t>
+          <t>('USA_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>371260</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>('RU', 'CR')</t>
+          <t>('EG_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>('CM', 'USA')</t>
+          <t>('RU_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -3266,14 +3266,14 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>('ME', 'QA')</t>
+          <t>('USA_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>0</v>
+        <v>39080</v>
       </c>
       <c r="D158" t="n">
-        <v>0</v>
+        <v>0.003908000390800039</v>
       </c>
     </row>
     <row r="159">
@@ -3284,14 +3284,14 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>('ME', 'CR')</t>
+          <t>('AU_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>0</v>
+        <v>119643.4077049121</v>
       </c>
       <c r="D159" t="n">
-        <v>0</v>
+        <v>0.01196434196692541</v>
       </c>
     </row>
     <row r="160">
@@ -3302,14 +3302,14 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>('USA', 'CM')</t>
+          <t>('QA_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>0</v>
+        <v>320873.6647387617</v>
       </c>
       <c r="D160" t="n">
-        <v>0</v>
+        <v>0.03208736968261314</v>
       </c>
     </row>
     <row r="161">
@@ -3320,14 +3320,14 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>155831.5</v>
+        <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0.01558315155831516</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -3428,14 +3428,14 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C167" t="n">
-        <v>0</v>
+        <v>79824.88002160867</v>
       </c>
       <c r="D167" t="n">
-        <v>0</v>
+        <v>0.007982488800409747</v>
       </c>
     </row>
     <row r="168">
@@ -3446,14 +3446,14 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C168" t="n">
-        <v>37827.32209085295</v>
+        <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>0.003782732587358553</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -3572,14 +3572,14 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>737432.8016467615</v>
+        <v>0</v>
       </c>
       <c r="D175" t="n">
-        <v>0.0737432875390049</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -3626,14 +3626,14 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>0</v>
+        <v>1536.335261238157</v>
       </c>
       <c r="D178" t="n">
-        <v>0</v>
+        <v>0.0001536335414871698</v>
       </c>
     </row>
     <row r="179">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -3662,7 +3662,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -3716,14 +3716,14 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>198733.9401997356</v>
+        <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01987339600731316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -3770,14 +3770,14 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>111378</v>
+        <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.01113780111378011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
@@ -3788,14 +3788,14 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>60574</v>
+        <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.006057400605740061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -3824,14 +3824,14 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>322409.9999999999</v>
+        <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.03224100322410031</v>
+        <v>0</v>
       </c>
     </row>
     <row r="190">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -3878,14 +3878,14 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>0</v>
+        <v>164190.907888464</v>
       </c>
       <c r="D192" t="n">
-        <v>0</v>
+        <v>0.01641909243075565</v>
       </c>
     </row>
     <row r="193">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -4022,14 +4022,14 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>81491.87295725508</v>
+        <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0.008149188110644318</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -4040,14 +4040,14 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>0</v>
+        <v>425972</v>
       </c>
       <c r="D201" t="n">
-        <v>0</v>
+        <v>0.04259720425972043</v>
       </c>
     </row>
     <row r="202">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -4094,7 +4094,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -4130,14 +4130,14 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>0</v>
+        <v>339902.243945254</v>
       </c>
       <c r="D206" t="n">
-        <v>0</v>
+        <v>0.03399022779354818</v>
       </c>
     </row>
     <row r="207">
@@ -4148,14 +4148,14 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>0</v>
+        <v>356106.0153598423</v>
       </c>
       <c r="D207" t="n">
-        <v>0</v>
+        <v>0.03561060509704474</v>
       </c>
     </row>
     <row r="208">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -4220,7 +4220,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -4292,14 +4292,14 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C215" t="n">
-        <v>28762.64096205891</v>
+        <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>0.00287626438383233</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -4328,14 +4328,14 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C217" t="n">
-        <v>25402</v>
+        <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.002540200254020025</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -4382,7 +4382,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -4418,14 +4418,14 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C222" t="n">
-        <v>3106.598932508001</v>
+        <v>25402</v>
       </c>
       <c r="D222" t="n">
-        <v>0.0003106599243167925</v>
+        <v>0.002540200254020025</v>
       </c>
     </row>
     <row r="223">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -4598,14 +4598,14 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C232" t="n">
-        <v>764279.938706647</v>
+        <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.07642800151346485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="233">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -4796,14 +4796,14 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C243" t="n">
-        <v>3613.770355847626</v>
+        <v>0</v>
       </c>
       <c r="D243" t="n">
-        <v>0.0003613770717224698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -4886,7 +4886,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -4904,14 +4904,14 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C249" t="n">
-        <v>0</v>
+        <v>53884.57737520695</v>
       </c>
       <c r="D249" t="n">
-        <v>0</v>
+        <v>0.005388458276366523</v>
       </c>
     </row>
     <row r="250">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -4940,14 +4940,14 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C251" t="n">
-        <v>0</v>
+        <v>60872.29289923003</v>
       </c>
       <c r="D251" t="n">
-        <v>0</v>
+        <v>0.006087229898645993</v>
       </c>
     </row>
     <row r="252">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -5102,14 +5102,14 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C260" t="n">
-        <v>0</v>
+        <v>1459821.818317179</v>
       </c>
       <c r="D260" t="n">
-        <v>0</v>
+        <v>0.1459821964299375</v>
       </c>
     </row>
     <row r="261">
@@ -5120,14 +5120,14 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C261" t="n">
-        <v>0</v>
+        <v>60574</v>
       </c>
       <c r="D261" t="n">
-        <v>0</v>
+        <v>0.006057400605740061</v>
       </c>
     </row>
     <row r="262">
@@ -5138,14 +5138,14 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C262" t="n">
-        <v>0</v>
+        <v>42780.12063085777</v>
       </c>
       <c r="D262" t="n">
-        <v>0</v>
+        <v>0.004278012490887026</v>
       </c>
     </row>
     <row r="263">
@@ -5156,14 +5156,14 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C263" t="n">
-        <v>0</v>
+        <v>766145.0242350447</v>
       </c>
       <c r="D263" t="n">
-        <v>0</v>
+        <v>0.07661451008495548</v>
       </c>
     </row>
     <row r="264">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -5318,7 +5318,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -5354,7 +5354,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -5390,14 +5390,14 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C276" t="n">
-        <v>0</v>
+        <v>5093.587087416308</v>
       </c>
       <c r="D276" t="n">
-        <v>0</v>
+        <v>0.0005093587596775068</v>
       </c>
     </row>
     <row r="277">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -5462,14 +5462,14 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'ES_LNG_imp')</t>
         </is>
       </c>
       <c r="C280" t="n">
-        <v>299342.373114435</v>
+        <v>0</v>
       </c>
       <c r="D280" t="n">
-        <v>0.02993424030486753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'JS_LNG_imp')</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'PL_LNG_imp')</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -5588,14 +5588,14 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C287" t="n">
-        <v>0</v>
+        <v>24754.98766700632</v>
       </c>
       <c r="D287" t="n">
-        <v>0</v>
+        <v>0.002475499014250534</v>
       </c>
     </row>
     <row r="288">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -5660,7 +5660,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -5714,14 +5714,14 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'IN_LNG_imp')</t>
         </is>
       </c>
       <c r="C294" t="n">
-        <v>525837.8320231684</v>
+        <v>113561.275976016</v>
       </c>
       <c r="D294" t="n">
-        <v>0.05258378846069569</v>
+        <v>0.01135612873321447</v>
       </c>
     </row>
     <row r="295">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'TR_LNG_imp')</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'HR_LNG_imp')</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -5840,14 +5840,14 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('TT_LNG_exp', 'LT_LNG_imp')</t>
         </is>
       </c>
       <c r="C301" t="n">
-        <v>73275</v>
+        <v>0</v>
       </c>
       <c r="D301" t="n">
-        <v>0.007327500732750073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -5858,14 +5858,14 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C302" t="n">
-        <v>0</v>
+        <v>86623.01233299368</v>
       </c>
       <c r="D302" t="n">
-        <v>0</v>
+        <v>0.008662302099529577</v>
       </c>
     </row>
     <row r="303">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'EG_LNG_imp')</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('RU_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -5912,14 +5912,14 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'EL_LNG_imp')</t>
         </is>
       </c>
       <c r="C305" t="n">
-        <v>0</v>
+        <v>73275</v>
       </c>
       <c r="D305" t="n">
-        <v>0</v>
+        <v>0.007327500732750073</v>
       </c>
     </row>
     <row r="306">
@@ -5930,14 +5930,14 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'BE_LNG_imp')</t>
         </is>
       </c>
       <c r="C306" t="n">
-        <v>36490.41771</v>
+        <v>0</v>
       </c>
       <c r="D306" t="n">
-        <v>0.003649042135904214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('AU_LNG_exp', 'AS_LNG_imp')</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('IM_LNG_exp', 'CN_LNG_imp')</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -5984,14 +5984,14 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C309" t="n">
-        <v>0</v>
+        <v>510971</v>
       </c>
       <c r="D309" t="n">
-        <v>0</v>
+        <v>0.05109710510971051</v>
       </c>
     </row>
     <row r="310">
@@ -6002,14 +6002,14 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('QA_LNG_exp', 'IT_LNG_imp')</t>
         </is>
       </c>
       <c r="C310" t="n">
-        <v>0</v>
+        <v>155831.5</v>
       </c>
       <c r="D310" t="n">
-        <v>0</v>
+        <v>0.01558315155831516</v>
       </c>
     </row>
     <row r="311">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'FR_LNG_imp')</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -6038,14 +6038,14 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'LT_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'NL_LNG_imp')</t>
         </is>
       </c>
       <c r="C312" t="n">
-        <v>0</v>
+        <v>122125</v>
       </c>
       <c r="D312" t="n">
-        <v>0</v>
+        <v>0.01221250122125012</v>
       </c>
     </row>
     <row r="313">
@@ -6056,7 +6056,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('USA_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('AF_LNG_exp', 'UK_LNG_imp')</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'PT_LNG_imp')</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -6110,14 +6110,14 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('EG_LNG_exp', 'AF_LNG_imp')</t>
         </is>
       </c>
       <c r="C316" t="n">
-        <v>7494.689125</v>
+        <v>0</v>
       </c>
       <c r="D316" t="n">
-        <v>0.0007494689874468988</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('ME_LNG_exp', 'SA_LNG_imp')</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -6146,14 +6146,14 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'FI_LNG_imp')</t>
+          <t>('AL_Prod', 'AL')</t>
         </is>
       </c>
       <c r="C318" t="n">
-        <v>11669.45083333333</v>
+        <v>555.86415</v>
       </c>
       <c r="D318" t="n">
-        <v>0.001166945200027853</v>
+        <v>5.558642055864206e-05</v>
       </c>
     </row>
     <row r="319">
@@ -6164,14 +6164,14 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('DZ_Prod', 'DZ')</t>
         </is>
       </c>
       <c r="C319" t="n">
-        <v>0</v>
+        <v>795518.4641249999</v>
       </c>
       <c r="D319" t="n">
-        <v>0</v>
+        <v>0.07955185436768543</v>
       </c>
     </row>
     <row r="320">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('AT_Prod', 'AT')</t>
         </is>
       </c>
       <c r="C320" t="n">
-        <v>99377.29394723289</v>
+        <v>7561.745519999999</v>
       </c>
       <c r="D320" t="n">
-        <v>0.009937730388496328</v>
+        <v>0.0007561746276174626</v>
       </c>
     </row>
     <row r="321">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('BY_Prod', 'BY')</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -6218,14 +6218,14 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('BE_Prod', 'BE')</t>
         </is>
       </c>
       <c r="C322" t="n">
-        <v>25402</v>
+        <v>57.64300000000001</v>
       </c>
       <c r="D322" t="n">
-        <v>0.002540200254020025</v>
+        <v>5.764300576430059e-06</v>
       </c>
     </row>
     <row r="323">
@@ -6236,14 +6236,14 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('BA_Prod', 'BA')</t>
         </is>
       </c>
       <c r="C323" t="n">
-        <v>0</v>
+        <v>2907.090436157109</v>
       </c>
       <c r="D323" t="n">
-        <v>0</v>
+        <v>0.0002907090726866182</v>
       </c>
     </row>
     <row r="324">
@@ -6254,14 +6254,14 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('BG_Prod', 'BG')</t>
         </is>
       </c>
       <c r="C324" t="n">
-        <v>0</v>
+        <v>531.00927</v>
       </c>
       <c r="D324" t="n">
-        <v>0</v>
+        <v>5.310093231009323e-05</v>
       </c>
     </row>
     <row r="325">
@@ -6272,14 +6272,14 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('HR_Prod', 'HR')</t>
         </is>
       </c>
       <c r="C325" t="n">
-        <v>304823.9999999999</v>
+        <v>8679.52145</v>
       </c>
       <c r="D325" t="n">
-        <v>0.03048240304824029</v>
+        <v>0.0008679522317952232</v>
       </c>
     </row>
     <row r="326">
@@ -6290,14 +6290,14 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('CZ_Prod', 'CZ')</t>
         </is>
       </c>
       <c r="C326" t="n">
-        <v>0</v>
+        <v>1915.65275</v>
       </c>
       <c r="D326" t="n">
-        <v>0</v>
+        <v>0.0001915652941565294</v>
       </c>
     </row>
     <row r="327">
@@ -6308,14 +6308,14 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('DK_Prod', 'DK')</t>
         </is>
       </c>
       <c r="C327" t="n">
-        <v>0</v>
+        <v>13947.07557</v>
       </c>
       <c r="D327" t="n">
-        <v>0</v>
+        <v>0.00139470769647077</v>
       </c>
     </row>
     <row r="328">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('EE_Prod', 'EE')</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('FI_Prod', 'FI')</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -6362,14 +6362,14 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('FR_Prod', 'FR')</t>
         </is>
       </c>
       <c r="C330" t="n">
-        <v>0</v>
+        <v>169.49973</v>
       </c>
       <c r="D330" t="n">
-        <v>0</v>
+        <v>1.694997469499747e-05</v>
       </c>
     </row>
     <row r="331">
@@ -6380,14 +6380,14 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'EE_LNG_imp')</t>
+          <t>('DE_Prod', 'DE')</t>
         </is>
       </c>
       <c r="C331" t="n">
-        <v>0</v>
+        <v>47618.98</v>
       </c>
       <c r="D331" t="n">
-        <v>0</v>
+        <v>0.004761898476189848</v>
       </c>
     </row>
     <row r="332">
@@ -6398,14 +6398,14 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('EL_Prod', 'EL')</t>
         </is>
       </c>
       <c r="C332" t="n">
-        <v>0</v>
+        <v>63.30960000000002</v>
       </c>
       <c r="D332" t="n">
-        <v>0</v>
+        <v>6.330960633096065e-06</v>
       </c>
     </row>
     <row r="333">
@@ -6416,14 +6416,14 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('HU_Prod', 'HU')</t>
         </is>
       </c>
       <c r="C333" t="n">
-        <v>0</v>
+        <v>16462.45</v>
       </c>
       <c r="D333" t="n">
-        <v>0</v>
+        <v>0.001646245164624516</v>
       </c>
     </row>
     <row r="334">
@@ -6434,14 +6434,14 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('IE_Prod', 'IE')</t>
         </is>
       </c>
       <c r="C334" t="n">
-        <v>0</v>
+        <v>19829.69027</v>
       </c>
       <c r="D334" t="n">
-        <v>0</v>
+        <v>0.001982969225296922</v>
       </c>
     </row>
     <row r="335">
@@ -6452,14 +6452,14 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'DE_LNG_imp')</t>
+          <t>('IT_Prod', 'IT')</t>
         </is>
       </c>
       <c r="C335" t="n">
-        <v>0</v>
+        <v>38415.64</v>
       </c>
       <c r="D335" t="n">
-        <v>0</v>
+        <v>0.003841564384156438</v>
       </c>
     </row>
     <row r="336">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('LV_Prod', 'LV')</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -6488,14 +6488,14 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('LY_Prod', 'LY')</t>
         </is>
       </c>
       <c r="C337" t="n">
-        <v>303112.4782752534</v>
+        <v>124076.1869468165</v>
       </c>
       <c r="D337" t="n">
-        <v>0.03031125085865042</v>
+        <v>0.01240761993544364</v>
       </c>
     </row>
     <row r="338">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('LT_Prod', 'LT')</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('LU_Prod', 'LU')</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -6542,14 +6542,14 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('MD_Prod', 'MD')</t>
         </is>
       </c>
       <c r="C340" t="n">
-        <v>43774.39964126465</v>
+        <v>0</v>
       </c>
       <c r="D340" t="n">
-        <v>0.004377440401870505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -6560,14 +6560,14 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('NL_Prod', 'NL')</t>
         </is>
       </c>
       <c r="C341" t="n">
-        <v>1029.285770988878</v>
+        <v>234149.02171</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0001029285873917465</v>
+        <v>0.02341490451249045</v>
       </c>
     </row>
     <row r="342">
@@ -6578,14 +6578,14 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('MK_Prod', 'MK')</t>
         </is>
       </c>
       <c r="C342" t="n">
-        <v>125165.8995882279</v>
+        <v>0</v>
       </c>
       <c r="D342" t="n">
-        <v>0.01251659121048192</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -6596,14 +6596,14 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('NO_Prod', 'NO')</t>
         </is>
       </c>
       <c r="C343" t="n">
-        <v>0</v>
+        <v>1135333.76309</v>
       </c>
       <c r="D343" t="n">
-        <v>0</v>
+        <v>0.1135333876623388</v>
       </c>
     </row>
     <row r="344">
@@ -6614,14 +6614,14 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('PL_Prod', 'PL')</t>
         </is>
       </c>
       <c r="C344" t="n">
-        <v>0</v>
+        <v>54642.4376</v>
       </c>
       <c r="D344" t="n">
-        <v>0</v>
+        <v>0.00546424430642443</v>
       </c>
     </row>
     <row r="345">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('PT_Prod', 'PT')</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -6650,14 +6650,14 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'SA_LNG_imp')</t>
+          <t>('RO_Prod', 'RO')</t>
         </is>
       </c>
       <c r="C346" t="n">
-        <v>0</v>
+        <v>88096.09</v>
       </c>
       <c r="D346" t="n">
-        <v>0</v>
+        <v>0.008809609880960988</v>
       </c>
     </row>
     <row r="347">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('RU_Prod', 'RU')</t>
         </is>
       </c>
       <c r="C347" t="n">
-        <v>0</v>
+        <v>6237623.82943702</v>
       </c>
       <c r="D347" t="n">
-        <v>0</v>
+        <v>0.6237624453199465</v>
       </c>
     </row>
     <row r="348">
@@ -6686,14 +6686,14 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('RS_Prod', 'RS')</t>
         </is>
       </c>
       <c r="C348" t="n">
-        <v>0</v>
+        <v>3995.929999999999</v>
       </c>
       <c r="D348" t="n">
-        <v>0</v>
+        <v>0.0003995930399593039</v>
       </c>
     </row>
     <row r="349">
@@ -6704,14 +6704,14 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('SK_Prod', 'SK')</t>
         </is>
       </c>
       <c r="C349" t="n">
-        <v>0</v>
+        <v>651.6687699999999</v>
       </c>
       <c r="D349" t="n">
-        <v>0</v>
+        <v>6.516688351668834e-05</v>
       </c>
     </row>
     <row r="350">
@@ -6722,14 +6722,14 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'IT_LNG_imp')</t>
+          <t>('SI_Prod', 'SI')</t>
         </is>
       </c>
       <c r="C350" t="n">
-        <v>0</v>
+        <v>52.11318</v>
       </c>
       <c r="D350" t="n">
-        <v>0</v>
+        <v>5.211318521131852e-06</v>
       </c>
     </row>
     <row r="351">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'BE_LNG_imp')</t>
+          <t>('CH_Prod', 'CH')</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -6758,14 +6758,14 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'PL_LNG_imp')</t>
+          <t>('TN_Prod', 'TN')</t>
         </is>
       </c>
       <c r="C352" t="n">
-        <v>0</v>
+        <v>18563</v>
       </c>
       <c r="D352" t="n">
-        <v>0</v>
+        <v>0.001856300185630018</v>
       </c>
     </row>
     <row r="353">
@@ -6776,14 +6776,14 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>('RU_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('TR_Prod', 'TR')</t>
         </is>
       </c>
       <c r="C353" t="n">
-        <v>0</v>
+        <v>4274.472699999999</v>
       </c>
       <c r="D353" t="n">
-        <v>0</v>
+        <v>0.0004274473127447312</v>
       </c>
     </row>
     <row r="354">
@@ -6794,14 +6794,14 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'LV_LNG_imp')</t>
+          <t>('UK_Prod', 'UK')</t>
         </is>
       </c>
       <c r="C354" t="n">
-        <v>0</v>
+        <v>320813.11304</v>
       </c>
       <c r="D354" t="n">
-        <v>0</v>
+        <v>0.03208131451213145</v>
       </c>
     </row>
     <row r="355">
@@ -6812,14 +6812,14 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>('USA_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('UA_Prod', 'UA')</t>
         </is>
       </c>
       <c r="C355" t="n">
-        <v>203896.5541182648</v>
+        <v>190671.32</v>
       </c>
       <c r="D355" t="n">
-        <v>0.02038965745079222</v>
+        <v>0.01906713390671339</v>
       </c>
     </row>
     <row r="356">
@@ -6830,14 +6830,14 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'ES_LNG_imp')</t>
+          <t>('ES_Prod', 'ES')</t>
         </is>
       </c>
       <c r="C356" t="n">
-        <v>0</v>
+        <v>449.42</v>
       </c>
       <c r="D356" t="n">
-        <v>0</v>
+        <v>4.494200449420045e-05</v>
       </c>
     </row>
     <row r="357">
@@ -6848,14 +6848,14 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'UK_LNG_imp')</t>
+          <t>('USA_Prod', 'USA')</t>
         </is>
       </c>
       <c r="C357" t="n">
-        <v>0</v>
+        <v>9035422.293721648</v>
       </c>
       <c r="D357" t="n">
-        <v>0</v>
+        <v>0.9035423197263968</v>
       </c>
     </row>
     <row r="358">
@@ -6866,14 +6866,14 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'FR_LNG_imp')</t>
+          <t>('CM_Prod', 'CM')</t>
         </is>
       </c>
       <c r="C358" t="n">
-        <v>0</v>
+        <v>1965121.004492735</v>
       </c>
       <c r="D358" t="n">
-        <v>0</v>
+        <v>0.1965121201004855</v>
       </c>
     </row>
     <row r="359">
@@ -6884,14 +6884,14 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'NL_LNG_imp')</t>
+          <t>('SA_Prod', 'SA')</t>
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0</v>
+        <v>1242293.419598245</v>
       </c>
       <c r="D359" t="n">
-        <v>0</v>
+        <v>0.1242293543827599</v>
       </c>
     </row>
     <row r="360">
@@ -6902,14 +6902,14 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>('IM_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('TT_Prod', 'TT')</t>
         </is>
       </c>
       <c r="C360" t="n">
-        <v>0</v>
+        <v>287875.6308585868</v>
       </c>
       <c r="D360" t="n">
-        <v>0</v>
+        <v>0.02878756596461528</v>
       </c>
     </row>
     <row r="361">
@@ -6920,14 +6920,14 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>('AF_LNG_exp', 'EG_LNG_imp')</t>
+          <t>('ME_Prod', 'ME')</t>
         </is>
       </c>
       <c r="C361" t="n">
-        <v>0</v>
+        <v>4816654.374502789</v>
       </c>
       <c r="D361" t="n">
-        <v>0</v>
+        <v>0.4816654856168275</v>
       </c>
     </row>
     <row r="362">
@@ -6938,14 +6938,14 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('QA_Prod', 'QA')</t>
         </is>
       </c>
       <c r="C362" t="n">
-        <v>0</v>
+        <v>1709113.365474044</v>
       </c>
       <c r="D362" t="n">
-        <v>0</v>
+        <v>0.1709113536385398</v>
       </c>
     </row>
     <row r="363">
@@ -6956,14 +6956,14 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'AS_LNG_imp')</t>
+          <t>('AF_Prod', 'AF')</t>
         </is>
       </c>
       <c r="C363" t="n">
-        <v>488874.328389118</v>
+        <v>756389.0043133288</v>
       </c>
       <c r="D363" t="n">
-        <v>0.04888743772765557</v>
+        <v>0.07563890799522367</v>
       </c>
     </row>
     <row r="364">
@@ -6974,14 +6974,14 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>('AU_LNG_exp', 'TR_LNG_imp')</t>
+          <t>('MA_Prod', 'MA')</t>
         </is>
       </c>
       <c r="C364" t="n">
-        <v>0</v>
+        <v>683.9</v>
       </c>
       <c r="D364" t="n">
-        <v>0</v>
+        <v>6.839000683900068e-05</v>
       </c>
     </row>
     <row r="365">
@@ -6992,14 +6992,14 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'AF_LNG_imp')</t>
+          <t>('AU_Prod', 'AU')</t>
         </is>
       </c>
       <c r="C365" t="n">
-        <v>0</v>
+        <v>1412790.118043227</v>
       </c>
       <c r="D365" t="n">
-        <v>0</v>
+        <v>0.1412790259322253</v>
       </c>
     </row>
     <row r="366">
@@ -7010,14 +7010,14 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'IN_LNG_imp')</t>
+          <t>('CN_Prod', 'CN')</t>
         </is>
       </c>
       <c r="C366" t="n">
-        <v>0</v>
+        <v>1895470.062684365</v>
       </c>
       <c r="D366" t="n">
-        <v>0</v>
+        <v>0.189547025223139</v>
       </c>
     </row>
     <row r="367">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'IE_LNG_imp')</t>
+          <t>('JS_Prod', 'JS')</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -7046,14 +7046,14 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'PT_LNG_imp')</t>
+          <t>('IN_Prod', 'IN')</t>
         </is>
       </c>
       <c r="C368" t="n">
-        <v>0</v>
+        <v>232141.3214433222</v>
       </c>
       <c r="D368" t="n">
-        <v>0</v>
+        <v>0.02321413446574567</v>
       </c>
     </row>
     <row r="369">
@@ -7064,14 +7064,14 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>('EG_LNG_exp', 'CN_LNG_imp')</t>
+          <t>('AS_Prod', 'AS')</t>
         </is>
       </c>
       <c r="C369" t="n">
-        <v>0</v>
+        <v>1514321.734984355</v>
       </c>
       <c r="D369" t="n">
-        <v>0</v>
+        <v>0.1514321886416544</v>
       </c>
     </row>
     <row r="370">
@@ -7082,14 +7082,14 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>('QA_LNG_exp', 'EL_LNG_imp')</t>
+          <t>('CR_Prod', 'CR')</t>
         </is>
       </c>
       <c r="C370" t="n">
-        <v>0</v>
+        <v>1660028.45956802</v>
       </c>
       <c r="D370" t="n">
-        <v>0</v>
+        <v>0.1660028625570882</v>
       </c>
     </row>
     <row r="371">
@@ -7100,14 +7100,14 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>('ME_LNG_exp', 'HR_LNG_imp')</t>
+          <t>('EG_Prod', 'EG')</t>
         </is>
       </c>
       <c r="C371" t="n">
-        <v>0</v>
+        <v>571204.751520874</v>
       </c>
       <c r="D371" t="n">
-        <v>0</v>
+        <v>0.05712048086413549</v>
       </c>
     </row>
     <row r="372">
@@ -7118,1040 +7118,14 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>('TT_LNG_exp', 'JS_LNG_imp')</t>
+          <t>('IM_Prod', 'IM')</t>
         </is>
       </c>
       <c r="C372" t="n">
-        <v>0</v>
+        <v>1346210.438308913</v>
       </c>
       <c r="D372" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B373" t="inlineStr">
-        <is>
-          <t>('QA_LNG_exp', 'LV_LNG_imp')</t>
-        </is>
-      </c>
-      <c r="C373" t="n">
-        <v>0</v>
-      </c>
-      <c r="D373" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B374" t="inlineStr">
-        <is>
-          <t>('QA_LNG_exp', 'FI_LNG_imp')</t>
-        </is>
-      </c>
-      <c r="C374" t="n">
-        <v>0</v>
-      </c>
-      <c r="D374" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B375" t="inlineStr">
-        <is>
-          <t>('AL_Prod', 'AL')</t>
-        </is>
-      </c>
-      <c r="C375" t="n">
-        <v>527.1012699999999</v>
-      </c>
-      <c r="D375" t="n">
-        <v>5.271013227101322e-05</v>
-      </c>
-    </row>
-    <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B376" t="inlineStr">
-        <is>
-          <t>('DZ_Prod', 'DZ')</t>
-        </is>
-      </c>
-      <c r="C376" t="n">
-        <v>992082.4375</v>
-      </c>
-      <c r="D376" t="n">
-        <v>0.09920825367082536</v>
-      </c>
-    </row>
-    <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B377" t="inlineStr">
-        <is>
-          <t>('AT_Prod', 'AT')</t>
-        </is>
-      </c>
-      <c r="C377" t="n">
-        <v>5354.663439999999</v>
-      </c>
-      <c r="D377" t="n">
-        <v>0.0005354663975466397</v>
-      </c>
-    </row>
-    <row r="378">
-      <c r="A378" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B378" t="inlineStr">
-        <is>
-          <t>('BY_Prod', 'BY')</t>
-        </is>
-      </c>
-      <c r="C378" t="n">
-        <v>0</v>
-      </c>
-      <c r="D378" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B379" t="inlineStr">
-        <is>
-          <t>('BE_Prod', 'BE')</t>
-        </is>
-      </c>
-      <c r="C379" t="n">
-        <v>146.55</v>
-      </c>
-      <c r="D379" t="n">
-        <v>1.465500146550015e-05</v>
-      </c>
-    </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B380" t="inlineStr">
-        <is>
-          <t>('BA_Prod', 'BA')</t>
-        </is>
-      </c>
-      <c r="C380" t="n">
-        <v>6983.598371601989</v>
-      </c>
-      <c r="D380" t="n">
-        <v>0.0006983599069961896</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B381" t="inlineStr">
-        <is>
-          <t>('BG_Prod', 'BG')</t>
-        </is>
-      </c>
-      <c r="C381" t="n">
-        <v>79.52780000000001</v>
-      </c>
-      <c r="D381" t="n">
-        <v>7.95278079527808e-06</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B382" t="inlineStr">
-        <is>
-          <t>('HR_Prod', 'HR')</t>
-        </is>
-      </c>
-      <c r="C382" t="n">
-        <v>7367.557</v>
-      </c>
-      <c r="D382" t="n">
-        <v>0.0007367557736755773</v>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B383" t="inlineStr">
-        <is>
-          <t>('CZ_Prod', 'CZ')</t>
-        </is>
-      </c>
-      <c r="C383" t="n">
-        <v>1821.80213</v>
-      </c>
-      <c r="D383" t="n">
-        <v>0.0001821802312180231</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B384" t="inlineStr">
-        <is>
-          <t>('DK_Prod', 'DK')</t>
-        </is>
-      </c>
-      <c r="C384" t="n">
-        <v>17600.3619</v>
-      </c>
-      <c r="D384" t="n">
-        <v>0.001760036366003637</v>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B385" t="inlineStr">
-        <is>
-          <t>('EE_Prod', 'EE')</t>
-        </is>
-      </c>
-      <c r="C385" t="n">
-        <v>0</v>
-      </c>
-      <c r="D385" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B386" t="inlineStr">
-        <is>
-          <t>('FI_Prod', 'FI')</t>
-        </is>
-      </c>
-      <c r="C386" t="n">
-        <v>0</v>
-      </c>
-      <c r="D386" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B387" t="inlineStr">
-        <is>
-          <t>('FR_Prod', 'FR')</t>
-        </is>
-      </c>
-      <c r="C387" t="n">
-        <v>120.91352</v>
-      </c>
-      <c r="D387" t="n">
-        <v>1.209135320913532e-05</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B388" t="inlineStr">
-        <is>
-          <t>('DE_Prod', 'DE')</t>
-        </is>
-      </c>
-      <c r="C388" t="n">
-        <v>37839.21</v>
-      </c>
-      <c r="D388" t="n">
-        <v>0.003783921378392138</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>('EL_Prod', 'EL')</t>
-        </is>
-      </c>
-      <c r="C389" t="n">
-        <v>19.45207</v>
-      </c>
-      <c r="D389" t="n">
-        <v>1.94520719452072e-06</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>('HU_Prod', 'HU')</t>
-        </is>
-      </c>
-      <c r="C390" t="n">
-        <v>16841.526</v>
-      </c>
-      <c r="D390" t="n">
-        <v>0.001684152768415277</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>('IE_Prod', 'IE')</t>
-        </is>
-      </c>
-      <c r="C391" t="n">
-        <v>10559.26945</v>
-      </c>
-      <c r="D391" t="n">
-        <v>0.001055927050592705</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B392" t="inlineStr">
-        <is>
-          <t>('IT_Prod', 'IT')</t>
-        </is>
-      </c>
-      <c r="C392" t="n">
-        <v>28726.18388</v>
-      </c>
-      <c r="D392" t="n">
-        <v>0.002872618675261868</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B393" t="inlineStr">
-        <is>
-          <t>('LV_Prod', 'LV')</t>
-        </is>
-      </c>
-      <c r="C393" t="n">
-        <v>0</v>
-      </c>
-      <c r="D393" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>('LY_Prod', 'LY')</t>
-        </is>
-      </c>
-      <c r="C394" t="n">
-        <v>159325.9949275718</v>
-      </c>
-      <c r="D394" t="n">
-        <v>0.01593260108601729</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>('LT_Prod', 'LT')</t>
-        </is>
-      </c>
-      <c r="C395" t="n">
-        <v>0</v>
-      </c>
-      <c r="D395" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>('LU_Prod', 'LU')</t>
-        </is>
-      </c>
-      <c r="C396" t="n">
-        <v>0</v>
-      </c>
-      <c r="D396" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B397" t="inlineStr">
-        <is>
-          <t>('MD_Prod', 'MD')</t>
-        </is>
-      </c>
-      <c r="C397" t="n">
-        <v>0</v>
-      </c>
-      <c r="D397" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B398" t="inlineStr">
-        <is>
-          <t>('NL_Prod', 'NL')</t>
-        </is>
-      </c>
-      <c r="C398" t="n">
-        <v>96124.81221000002</v>
-      </c>
-      <c r="D398" t="n">
-        <v>0.00961248218224822</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B399" t="inlineStr">
-        <is>
-          <t>('MK_Prod', 'MK')</t>
-        </is>
-      </c>
-      <c r="C399" t="n">
-        <v>0</v>
-      </c>
-      <c r="D399" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="400">
-      <c r="A400" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B400" t="inlineStr">
-        <is>
-          <t>('NO_Prod', 'NO')</t>
-        </is>
-      </c>
-      <c r="C400" t="n">
-        <v>1152595.28185</v>
-      </c>
-      <c r="D400" t="n">
-        <v>0.115259539710954</v>
-      </c>
-    </row>
-    <row r="401">
-      <c r="A401" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B401" t="inlineStr">
-        <is>
-          <t>('PL_Prod', 'PL')</t>
-        </is>
-      </c>
-      <c r="C401" t="n">
-        <v>35142.81676750333</v>
-      </c>
-      <c r="D401" t="n">
-        <v>0.003514282028178536</v>
-      </c>
-    </row>
-    <row r="402">
-      <c r="A402" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B402" t="inlineStr">
-        <is>
-          <t>('PT_Prod', 'PT')</t>
-        </is>
-      </c>
-      <c r="C402" t="n">
-        <v>0</v>
-      </c>
-      <c r="D402" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B403" t="inlineStr">
-        <is>
-          <t>('RO_Prod', 'RO')</t>
-        </is>
-      </c>
-      <c r="C403" t="n">
-        <v>91564.43999999999</v>
-      </c>
-      <c r="D403" t="n">
-        <v>0.00915644491564449</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B404" t="inlineStr">
-        <is>
-          <t>('RU_Prod', 'RU')</t>
-        </is>
-      </c>
-      <c r="C404" t="n">
-        <v>5728954.09275353</v>
-      </c>
-      <c r="D404" t="n">
-        <v>0.5728954665648996</v>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B405" t="inlineStr">
-        <is>
-          <t>('RS_Prod', 'RS')</t>
-        </is>
-      </c>
-      <c r="C405" t="n">
-        <v>2882.15</v>
-      </c>
-      <c r="D405" t="n">
-        <v>0.0002882150288215029</v>
-      </c>
-    </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr">
-        <is>
-          <t>('SK_Prod', 'SK')</t>
-        </is>
-      </c>
-      <c r="C406" t="n">
-        <v>391.16149</v>
-      </c>
-      <c r="D406" t="n">
-        <v>3.911615291161529e-05</v>
-      </c>
-    </row>
-    <row r="407">
-      <c r="A407" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B407" t="inlineStr">
-        <is>
-          <t>('SI_Prod', 'SI')</t>
-        </is>
-      </c>
-      <c r="C407" t="n">
-        <v>37.14554</v>
-      </c>
-      <c r="D407" t="n">
-        <v>3.714554371455437e-06</v>
-      </c>
-    </row>
-    <row r="408">
-      <c r="A408" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B408" t="inlineStr">
-        <is>
-          <t>('CH_Prod', 'CH')</t>
-        </is>
-      </c>
-      <c r="C408" t="n">
-        <v>0</v>
-      </c>
-      <c r="D408" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="409">
-      <c r="A409" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B409" t="inlineStr">
-        <is>
-          <t>('TN_Prod', 'TN')</t>
-        </is>
-      </c>
-      <c r="C409" t="n">
-        <v>18008.064</v>
-      </c>
-      <c r="D409" t="n">
-        <v>0.001800806580080658</v>
-      </c>
-    </row>
-    <row r="410">
-      <c r="A410" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B410" t="inlineStr">
-        <is>
-          <t>('TR_Prod', 'TR')</t>
-        </is>
-      </c>
-      <c r="C410" t="n">
-        <v>22071.5047</v>
-      </c>
-      <c r="D410" t="n">
-        <v>0.002207150690715069</v>
-      </c>
-    </row>
-    <row r="411">
-      <c r="A411" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B411" t="inlineStr">
-        <is>
-          <t>('UK_Prod', 'UK')</t>
-        </is>
-      </c>
-      <c r="C411" t="n">
-        <v>336803.220666</v>
-      </c>
-      <c r="D411" t="n">
-        <v>0.03368032543463254</v>
-      </c>
-    </row>
-    <row r="412">
-      <c r="A412" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B412" t="inlineStr">
-        <is>
-          <t>('UA_Prod', 'UA')</t>
-        </is>
-      </c>
-      <c r="C412" t="n">
-        <v>172908.3456243854</v>
-      </c>
-      <c r="D412" t="n">
-        <v>0.01729083629152217</v>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr">
-        <is>
-          <t>('ES_Prod', 'ES')</t>
-        </is>
-      </c>
-      <c r="C413" t="n">
-        <v>209.71305</v>
-      </c>
-      <c r="D413" t="n">
-        <v>2.097130709713071e-05</v>
-      </c>
-    </row>
-    <row r="414">
-      <c r="A414" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B414" t="inlineStr">
-        <is>
-          <t>('USA_Prod', 'USA')</t>
-        </is>
-      </c>
-      <c r="C414" t="n">
-        <v>9999999</v>
-      </c>
-      <c r="D414" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>('CM_Prod', 'CM')</t>
-        </is>
-      </c>
-      <c r="C415" t="n">
-        <v>2132790.764230879</v>
-      </c>
-      <c r="D415" t="n">
-        <v>0.2132790977509977</v>
-      </c>
-    </row>
-    <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B416" t="inlineStr">
-        <is>
-          <t>('SA_Prod', 'SA')</t>
-        </is>
-      </c>
-      <c r="C416" t="n">
-        <v>1338762.310771848</v>
-      </c>
-      <c r="D416" t="n">
-        <v>0.1338762444648093</v>
-      </c>
-    </row>
-    <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B417" t="inlineStr">
-        <is>
-          <t>('TT_Prod', 'TT')</t>
-        </is>
-      </c>
-      <c r="C417" t="n">
-        <v>244187.5310400494</v>
-      </c>
-      <c r="D417" t="n">
-        <v>0.02441875554588049</v>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B418" t="inlineStr">
-        <is>
-          <t>('ME_Prod', 'ME')</t>
-        </is>
-      </c>
-      <c r="C418" t="n">
-        <v>5194976.912176006</v>
-      </c>
-      <c r="D418" t="n">
-        <v>0.5194977431673748</v>
-      </c>
-    </row>
-    <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B419" t="inlineStr">
-        <is>
-          <t>('QA_Prod', 'QA')</t>
-        </is>
-      </c>
-      <c r="C419" t="n">
-        <v>1768141.250753962</v>
-      </c>
-      <c r="D419" t="n">
-        <v>0.1768141427568105</v>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>('AF_Prod', 'AF')</t>
-        </is>
-      </c>
-      <c r="C420" t="n">
-        <v>750869.2287163949</v>
-      </c>
-      <c r="D420" t="n">
-        <v>0.07508693038033253</v>
-      </c>
-    </row>
-    <row r="421">
-      <c r="A421" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B421" t="inlineStr">
-        <is>
-          <t>('MA_Prod', 'MA')</t>
-        </is>
-      </c>
-      <c r="C421" t="n">
-        <v>683.9</v>
-      </c>
-      <c r="D421" t="n">
-        <v>6.839000683900068e-05</v>
-      </c>
-    </row>
-    <row r="422">
-      <c r="A422" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B422" t="inlineStr">
-        <is>
-          <t>('AU_Prod', 'AU')</t>
-        </is>
-      </c>
-      <c r="C422" t="n">
-        <v>1129419.886368038</v>
-      </c>
-      <c r="D422" t="n">
-        <v>0.1129419999310038</v>
-      </c>
-    </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>('CN_Prod', 'CN')</t>
-        </is>
-      </c>
-      <c r="C423" t="n">
-        <v>2288704.156833825</v>
-      </c>
-      <c r="D423" t="n">
-        <v>0.2288704385704264</v>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>('JS_Prod', 'JS')</t>
-        </is>
-      </c>
-      <c r="C424" t="n">
-        <v>0</v>
-      </c>
-      <c r="D424" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>('IN_Prod', 'IN')</t>
-        </is>
-      </c>
-      <c r="C425" t="n">
-        <v>308590.2229916077</v>
-      </c>
-      <c r="D425" t="n">
-        <v>0.03085902538506331</v>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>('AS_Prod', 'AS')</t>
-        </is>
-      </c>
-      <c r="C426" t="n">
-        <v>1259517.180291699</v>
-      </c>
-      <c r="D426" t="n">
-        <v>0.125951730624343</v>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>('CR_Prod', 'CR')</t>
-        </is>
-      </c>
-      <c r="C427" t="n">
-        <v>1828659.302226193</v>
-      </c>
-      <c r="D427" t="n">
-        <v>0.1828659485092141</v>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>('EG_Prod', 'EG')</t>
-        </is>
-      </c>
-      <c r="C428" t="n">
-        <v>557871.0357303467</v>
-      </c>
-      <c r="D428" t="n">
-        <v>0.05578710915174558</v>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>Methane</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>('IM_Prod', 'IM')</t>
-        </is>
-      </c>
-      <c r="C429" t="n">
-        <v>1419953.943201544</v>
-      </c>
-      <c r="D429" t="n">
-        <v>0.1419954085196952</v>
+        <v>0.134621057292997</v>
       </c>
     </row>
   </sheetData>
